--- a/Bonds/bonds.xlsx
+++ b/Bonds/bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ilya\Documents\GitHub\projects\Bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89AB08BB-17EA-413E-86B4-DB1B20D77071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9ADF0EB-355E-4B09-8B7A-DCC626ECD787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C1DB8464-260E-4338-9640-726B3E736107}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="230">
   <si>
     <t>Характеристики Вклада</t>
   </si>
@@ -97,6 +97,624 @@
   </si>
   <si>
     <t>Продать не ниже, в %</t>
+  </si>
+  <si>
+    <t>Металлоинвест ХК-002P-04 ISIN: RU000A10E7W8 AA /AAA (АКРА/НКР) Ориентир купона: ФИНАЛ = КС+1.85 (было КС + не более 2%) каждые 30 дней Без оферт 4 года до погашения: 08.02.2030 Сбор заявок 03.02.26 Начало торгов - 9 февраля</t>
+  </si>
+  <si>
+    <t>RU000A10E7W8</t>
+  </si>
+  <si>
+    <t>A101-50-001P-02 Номинал: 1000 Р Объем: 3 млрд Р (на оба выпуска) Погашение: через 2 года Купон: ФИНАЛ 17% (18% (YTM 19,56%)) Выплаты: 12 раз в год Амортизация: Нет Оферта: Нет Рейтинг: A+(RU) AKPA / ruA+ Эксперт PA / A+.ru HKP Размещение: 26 декабря 2025 года</t>
+  </si>
+  <si>
+    <t>RU000A10DZU7</t>
+  </si>
+  <si>
+    <t>A101-50-001P-03 Номинал: 1000 Р Погашение: через 2 года Купон: ФИНАЛ КС +400 (КС +450 б.п.) Выплаты: 12 раз в год Амортизация: Нет Оферта: Нет Рейтинг: A+(RU) AKPA / ruA+ Эксперт PA / A+.ru HKP Только для квалов: Да Сбор заявок: 24 декабря 2025 года Размещение: 26 декабря 2025 года</t>
+  </si>
+  <si>
+    <t>RU000A10DZT9</t>
+  </si>
+  <si>
+    <t>АЛРОСА 001P-02. RU000A109SH2. Взял с рынка по цене 1000.6 руб. Купон ежм КС+1.14%. (Доходность 19.21% при кс=17%). ОСТАЛОСЬ 5 МЕС ДО ПОГАШЕНИЯ.</t>
+  </si>
+  <si>
+    <t>RU000A109SH2</t>
+  </si>
+  <si>
+    <t>АЛРОСА 001Р-01 RU000A109L49 (взял с рынка по 99.82%) КС+1.2% ежм на 3 не полных года без оферты и амортизации</t>
+  </si>
+  <si>
+    <t>RU000A109L49</t>
+  </si>
+  <si>
+    <t>АО «ПГК» 003Р-02 (фикс) RU000A10DSL1 - Дата размещения: 12 декабря 2025 года Рейтинг: АА, прогноз «стабильный» (Эксперт РА) Купон ежемесячный: фикс ФИНАЛ= 15.95% (было не выше КБД (3,3 года) + 275 б.п. = до 17.3%) Срок: 3,3 года фикс Объем: до 20 млрд руб. Амортизация: нет ОФЕРТА PUT: 29.03.29 Можно ПРОДАТЬ после 12.12.28 с ЛДВ Номинал: 1000 руб. !!! Внимание !!! ОФЕРТА PUT: 29.03.29 Погашение: 16.11.30</t>
+  </si>
+  <si>
+    <t>RU000A10DSL1</t>
+  </si>
+  <si>
+    <t>АФК Система 002P-05 $RU000A10CU55 Рейтинг: АА- - Купон: ключевая ставка ЦБ+3,5% - Частота выплат: 12 раз в ГОД - КУПИЛ с рынка по цене цена: 993,7Р - Дата погашения: 16.09.2027</t>
+  </si>
+  <si>
+    <t>RU000A10CU55</t>
+  </si>
+  <si>
+    <t>Акции ВК RU000A106YF0 (взамен на иностранные бумаги)</t>
+  </si>
+  <si>
+    <t>RU000A106YF0</t>
+  </si>
+  <si>
+    <t>Акции Лента RU000A102S15 (взамен на иностранные бумаги)</t>
+  </si>
+  <si>
+    <t>RU000A102S15</t>
+  </si>
+  <si>
+    <t>Атомэнергопром Атомэнп-001P-10 Рейтинг: ААА (АКРА, прогноз «Стабильный») Купон: ФИНАЛ 15.15% КБД (5.5 лет)+150 б.п.= 15.15 (квартальный) Срок обращения: 5.5 лет Объем: 25 млрд. Р Амортизация: нет Оферта: нет Номинал: 1000 Р Размещение 24 декабря</t>
+  </si>
+  <si>
+    <t>RU000A10DYG9</t>
+  </si>
+  <si>
+    <t>Атомэнергопром (001P-11) - Купон: ФИНАЛ = 14.7%. Фиксированный, Было: КБД (3 года 9 мес.) + премия до 150 б.п. (ожидаемо ~15,4%, YTM до 16,2%) Ежеквартально - Погашение: 07.12.2029 (срок 3 года 9 месяцев) - Рейтинг: ruAAA (Эксперт РА) - Амортизация: Нет Оферта: Нет Объем выпуска: 30 млрд руб. - Прием заявок: С 11 марта 2026, размещение 13 марта 2026</t>
+  </si>
+  <si>
+    <t>RU000A10EJQ7</t>
+  </si>
+  <si>
+    <t>Атомэнергопром 001Р-09 RU000A10DPS2 с фиксированным купоном ФИНАЛ 15.10 (было 15.0-16.4%) на 5 лет без оферты и амортизации. Выплата каждый квартал в марте, июне, сентябре и декабре Погашение 29.05.31</t>
+  </si>
+  <si>
+    <t>RU000A10DPS2</t>
+  </si>
+  <si>
+    <t>Балтийский лизинг Б0-П16 RU000A10BJX9 на 2 года 11 месяцев. Первичное размещение под 22.5-23%. Выплата каждые 30 дней</t>
+  </si>
+  <si>
+    <t>RU000A10BJX9</t>
+  </si>
+  <si>
+    <t>Балтийский лизинг Б0-П19 АА- на 3 года. Первичное размещение под 17%. Выплата каждые 30 дней Оферта CALL 27.08.28. Дата погашения 21.08.35</t>
+  </si>
+  <si>
+    <t>RU000A10СС32</t>
+  </si>
+  <si>
+    <t>ВТБ Лизинг 001Р-МБ-03 АА RU000A10CQE2 на 3 года. Первичное размещение под 15.5%. Выплата каждые 30 дней. Амортизация каждые 3 мес по 8.3%. Оферты нет</t>
+  </si>
+  <si>
+    <t>RU000A10CQE2</t>
+  </si>
+  <si>
+    <t>ВЭБ-002P-54B Купон: 7.50% (ежемесячный) Срок обращения: 5 лет Объем: 300 млн. $ Амортизация: нет Оферта: нет Номинал: 1000 $</t>
+  </si>
+  <si>
+    <t>RU000A10CTX6</t>
+  </si>
+  <si>
+    <t>ВЭБ-РФ 002P-36 ● ISIN: RU000A105YH8 ● Купон: RUONIA+170 б.п. . на 5 лет ● Выплат в год: 4 (март, июнь, сентябрь, декабрь) ● Погашение: 18.09.2030 ● Рейтинг: ААA от АКРА и Эксперт НА Без оферты и амортизации Купил 06.11.25 с рынка по цене 98.81%</t>
+  </si>
+  <si>
+    <t>RU000A105YH8</t>
+  </si>
+  <si>
+    <t>ГК Азот-001P-02 Рейтинг: А+ (Эксперт РА, прогноз «Стабильный») Купон: ФИНАЛ 16.5 (было до 17.25%) (ежемесячный) Срок обращения: 5 лет Объем: 5 млрд. Р Амортизация: нет !!!!!!!!!!!!!!!!!! Оферта: да (Пут через 2 года, 720 дней = 10.02.28) !!!!!!!!!!!!!!!!! Номинал: 1000 Р Сбор заявок 17 февраля 11:00-15:00 размещение 20 февраля Погашение 20.02.31</t>
+  </si>
+  <si>
+    <t>RU000A10EA40</t>
+  </si>
+  <si>
+    <t>ГК ПИОНЕР 002P-03 А (АКРА, Эксперт, НКР) Только для квалов Ориентир купона: ФИНАЛ КС + 4.5% (было не более 4,5%) [30 дней) Без оферт 3 года до погашения Начало торгов - 11 марта</t>
+  </si>
+  <si>
+    <t>RU000A10EHJ6</t>
+  </si>
+  <si>
+    <t>ГТЛК 001Р-22 - Купон: финал = 9.5% (было до 9,50%). Купон=0.78$ Номинал 100$ Фиксированный с привязкой к USD. Выплаты в рублях по курсу ЦБ. - Выплаты: Ежемесячно - Погашение: 3,5 года - Рейтинг: АА- (стабильный, АКРА и Эксперт РА) - Амортизация: По 50% номинала на 39-й и 43-й купоны - Оферта: Нет - Объем выпуска: Не менее 100 млн USD - Прием заявок: До 12 февраля 2026 г. Размещение 17.02.26</t>
+  </si>
+  <si>
+    <t>RU000A10EAM5</t>
+  </si>
+  <si>
+    <t>Газпром капитал БО-003Р-06 на 2 года под 17.5-18.5% (финал=КС+1.4) ежм без оферты и амортизации</t>
+  </si>
+  <si>
+    <t>RUO00A10D2Q2</t>
+  </si>
+  <si>
+    <t>Газпром нефть 005P-01R USD RU000A10D483 под 5.5-7.75% (ФИНАЛ 7.5%) ежм на 3.5 года без оферты и амортизации. Номинал 1000 USD</t>
+  </si>
+  <si>
+    <t>RU000A10D483</t>
+  </si>
+  <si>
+    <t>Газпром нефть 005P-02R ГaзпpHeф-005P-02R RU000A10DA66 под ФИНАЛ= (кс + 150) ежм на 3.5 года без оферты и амортизации. Номинал 1000 руб</t>
+  </si>
+  <si>
+    <t>RU000A10DA66</t>
+  </si>
+  <si>
+    <t>Газпром нефть БО 003P-14R ISIN: RU000A10BK09 • Купон: КС+200 б.п. • Текущая цена: 100,98% CY: 18,32% • Выплат в год: 12 ► Погашение: 27.04.2027 • Рейтинг: ААА от АКРА и Эксперт НА Взял с рынка по цене 100.82%</t>
+  </si>
+  <si>
+    <t>RU000A10BK09</t>
+  </si>
+  <si>
+    <t>Группа ЛСР БО 001Р- 11. На 3 года под 16.25-17.25 ежм (финал 16%). Без оферты. Амортизация по 30% на 24 и 30 купонах.</t>
+  </si>
+  <si>
+    <t>RU000A10CKY3</t>
+  </si>
+  <si>
+    <t>Дельтализинг 001Р-03 RU000A10DHT7 - Купон: 17.15% - Выплаты: ежемесячно - Погашение: через 3 года - Рейтинг: АА- - Амортизация: 4% номинала с 12-го купона ежемесячно - Оферта: нет</t>
+  </si>
+  <si>
+    <t>RU000A10DHT7</t>
+  </si>
+  <si>
+    <t>Денежный рынок Альфа-Капитал. АКММ. Ставка около КС РФ.</t>
+  </si>
+  <si>
+    <t>RU000A104X08</t>
+  </si>
+  <si>
+    <t>Денежный рынок Альфа-Капитал. АКММ. Ставка около КС РФ. Портфель ..40512</t>
+  </si>
+  <si>
+    <t>Денежный рынок Альфа-Капитал. АКММ. Ставка около КС РФ. Портфель ..7040</t>
+  </si>
+  <si>
+    <t>Денежный рынок. TMON</t>
+  </si>
+  <si>
+    <t>RU000A106DL2</t>
+  </si>
+  <si>
+    <t>Департамент финансов ЯНАО. RU000A10DMS9 Купон: ФИНАЛ КС+150 (было до КС+200 б.п.) Выплаты: 12 раз в год Срок: 3 года Оферта: нет • Рейтинг: ААА от АКРА Амортизация: 50% от номинала в дату выплаты 24 купона Сбор заявок - 27 ноября, размещение - 2 декабря 2025.</t>
+  </si>
+  <si>
+    <t>RU000A10DMS9</t>
+  </si>
+  <si>
+    <t>Инарктика 002P-04: • Рейтинг: A+(RU), прогноз «Стабильный» (АКРА) Номинал: 1000Р Срок обращения: 3 года • Купон: ФИНАЛ =15.75 (было не выше 18% годовых) • Периодичность выплат: ежемесячно • Амортизация: отсутствует Оферта: нет</t>
+  </si>
+  <si>
+    <t>RU000A10DHX9</t>
+  </si>
+  <si>
+    <t>Инарктика 002P-05: • Рейтинг: A+(RU), прогноз «Стабильный» (АКРА) Номинал: 1000Р Срок обращения: 3 года • Купон: ФИНАЛ КС+290 (было не выше КС+300 б. п.) годовых • Периодичность выплат: ежемесячно • Амортизация: отсутствует Оферта: нет</t>
+  </si>
+  <si>
+    <t>RU000A10DHV3</t>
+  </si>
+  <si>
+    <t>Кредитный Поток 3.0 RU000A10DBM5— это облигации, обеспеченные портфелем кредитных карт Т-Банка. Под 17,3% фикс ЕЖМ каждого 24 числа месяца на 25 месяцев. Оферта Call 24.12.27 на весь объём. При отсутствии оферты начнётся амортизация до 24.06.2030</t>
+  </si>
+  <si>
+    <t>RU000A0DBM5</t>
+  </si>
+  <si>
+    <t>Магнит ПАО БО-005P-04 Рейтинг: ААА (АКРА, прогноз «Стабильный») Купон: КС+150 б.п. финальный (ежемесячный) Срок обращения: 2 года Объем: 10 млрд. Р Амортизация: нет Оферта: нет Номинал: 1000 Р</t>
+  </si>
+  <si>
+    <t>RU000A10DDU4</t>
+  </si>
+  <si>
+    <t>Новабев Групп 003Р-02 RU000SYNG3P2 Объем: 3 млрд Р Купон: ФИНАЛ = 15.25% (было до 16% (YTM до 17,23%)) Выплаты: 12 раз в год Срок: 3 года (1080 дней) до 20.01.29 Оферта: нет Рейтинг: АА от ЭкспертРА и НКР Амортизация: 50% от номинала в дату выплаты 30 купона. Сбор заявок - 2 февраля, размещение - 5 февраля 2026.</t>
+  </si>
+  <si>
+    <t>RU000SYNG3P2</t>
+  </si>
+  <si>
+    <t>ОФЗ 26248. Купон 12.25% Выплата купонов 2 раза в год в июне и декабре по 61.08 руб</t>
+  </si>
+  <si>
+    <t>RU000A108EH4</t>
+  </si>
+  <si>
+    <t>ОФЗ 26250. RU000A10BVH7 . Купон 12%. Выплата купонов 2 раза в год в июне и декабре</t>
+  </si>
+  <si>
+    <t>RU000A10BVH7</t>
+  </si>
+  <si>
+    <t>ОФЗ 26253 на 13 лет. Купон 13%. Выплата купонов 2 раза в год в апреле и октябре</t>
+  </si>
+  <si>
+    <t>RU000A10D517</t>
+  </si>
+  <si>
+    <t>Новабев групп 002Р БО-П07 под кс+1.4% ежм на неполных 2 года. Без оферты и амортизации. Облигации (с рынка)</t>
+  </si>
+  <si>
+    <t>RU000A1099A2</t>
+  </si>
+  <si>
+    <t>Selectel (Селектел 001P-06R) на 2.5 года под 15.4% (на размещении 15-16.5%) с ежм выплатой. Без оферты и амортизации</t>
+  </si>
+  <si>
+    <t>RU000A10CU89</t>
+  </si>
+  <si>
+    <t>ЕвразХолдинг 003Р-05 USD на 3 года. Первичное размещение под 8.25% по курсу ЦБ в долларах. Выплата купона каждые 30 дней в рублях по курсу ЦБ. Стоимость одной облигации 100$. Без оферты и амортизации.</t>
+  </si>
+  <si>
+    <t>RU000A10D806</t>
+  </si>
+  <si>
+    <t>Облигации USD Полипласт П02-БО-06 USD на 2.5 года. Первичное размещение под 12.5-13% ФИНАЛ 12.95 по курсу ЦБ в долларах. Выплата купона каждые 30 дней в рублях по курсу ЦБ. Стоимость одной облигации 100$</t>
+  </si>
+  <si>
+    <t>RU000A10BU07</t>
+  </si>
+  <si>
+    <t>Облигации USD Полипласт П02-БО-06 USD на 2.5 года. Первичное размещение под 12.5-13% по курсу ЦБ в долларах. Выплата купона каждые 30 дней в рублях по курсу ЦБ. Стоимость одной облигации 100$</t>
+  </si>
+  <si>
+    <t>Облигации USD Полипласт П02-БО-09 USD RU000A10CH11 на 2.5 года. Первичное размещение под 11.25% по курсу ЦБ в долларах. Выплата купона каждые 30 дней в рублях по курсу ЦБ. Стоимость одной облигации 100$</t>
+  </si>
+  <si>
+    <t>RU000A10CH11</t>
+  </si>
+  <si>
+    <t>ВУШ 001Р-04. Whoosh. Купон ФИНАЛ=20.25% (было 21.5-22%) каждые 30 дней, на 3 года. Без оферты и амортизации</t>
+  </si>
+  <si>
+    <t>RU000A10BS76</t>
+  </si>
+  <si>
+    <t>АФК СИСТЕМА 002Р-02 под 22.75% ежм. Без оферты, без амортизации. На 2 года</t>
+  </si>
+  <si>
+    <t>RU000A10BPZ1</t>
+  </si>
+  <si>
+    <t>АФК СИСТЕМА 002Р-03. На 1 год и 8 месяцев под 22-22.5%. Размещение 2 июля. Финальная ставка 21.5%</t>
+  </si>
+  <si>
+    <t>RU000A10BY94</t>
+  </si>
+  <si>
+    <t>Облигации Атомэнергопром 001Р-07 RU000A10C6L5 с фиксированным купоном 14.35% на 5 лет без оферты и амортизации. Выплата каждый квартал в январе, апреле, июле, октябре</t>
+  </si>
+  <si>
+    <t>RU000A10C6L5</t>
+  </si>
+  <si>
+    <t>Облигации Атомэнергопром 001Р-08 RU000A10CT33 на 5 лет под 14.7% КБД (за 5 лет)+1.5%, без оферты и амортизации. Выплата каждый квартал: в марте, июне, сентябре и декабре.</t>
+  </si>
+  <si>
+    <t>RU000A10CT33</t>
+  </si>
+  <si>
+    <t>Облигации Атомэнергопром 001Р-09 RU000A10DPS2 с фиксированным купоном ФИНАЛ 15.10 (было 15.0-16.4%) на 5 лет без оферты и амортизации. Выплата каждый квартал в марте, июне, сентябре и декабре Погашение 29.05.31</t>
+  </si>
+  <si>
+    <t>Облигации Аэрофлот П02-БО-02 AFLTP02BO02 RU000A10CS75. под КС+1.6% ежм на 5 лет без оферты и амортизации.</t>
+  </si>
+  <si>
+    <t>RU000A10CS75</t>
+  </si>
+  <si>
+    <t>Аэрофлот выпуск 1. Купон 8.35% 4 раза в год. Март, июнь, сентябрь, декабрь</t>
+  </si>
+  <si>
+    <t>RU000A103943</t>
+  </si>
+  <si>
+    <t>Облигации ВТБ Лизинг 001Р-МБ-04 АА RU000VTBL1P4 на 3 года. Первичное размещение под 16.5%. Выплата каждые 30 дней. Амортизация каждые 3 мес по 8%, при завершении ещё 12%. Оферты нет. Размещение 16.12.25</t>
+  </si>
+  <si>
+    <t>RU000VTBL1P4</t>
+  </si>
+  <si>
+    <t>Облигации ГМК Норникель БО-001P-14-USD под 6.5-7% (финал 6.4%) ежм на 4 года без оферты и амортизации.</t>
+  </si>
+  <si>
+    <t>RU000A10CRC4</t>
+  </si>
+  <si>
+    <t>ГМК Норникель БО-001P-14-USD под 6.5-7% (финал 6.4%) ежм на 4 года без оферты и амортизации.</t>
+  </si>
+  <si>
+    <t>ИЭК Холдинг 001Р-04 (А-) на 2 года под КС+2.75% ежм (размещение было до КС+3.25), без амортизации, без оферты. Только для квалиф. инвесторов</t>
+  </si>
+  <si>
+    <t>RU000A10CZ43</t>
+  </si>
+  <si>
+    <t>Облигации МСП Факторинг 001Р-01 RU000A10D7Z2 на 2 года под КС+300 (19.5% при КС=16.5%) ЕЖМ без оферты и амортизации</t>
+  </si>
+  <si>
+    <t>RU000A10D7Z2</t>
+  </si>
+  <si>
+    <t>Облигации МСП Факторинг 001Р-01 RU000A10D7Z2 на 2 года под КС+300 (19.5% при КС=16.5%) ЕЖМ без оферты и амортизации. Взял с рынка</t>
+  </si>
+  <si>
+    <t>Облигации Новые технологии (А-) Нов Техн-001P-08 RU000A10CMQ5 на 2 года под 18-19% (ФИНАЛ 17%) ежм, без амортизации, без оферты</t>
+  </si>
+  <si>
+    <t>RU000A10CMQ5</t>
+  </si>
+  <si>
+    <t>ОФЗ 26226. Купон 7.95 в апреле и октябре</t>
+  </si>
+  <si>
+    <t>RU000A0ZZYW2</t>
+  </si>
+  <si>
+    <t>ОФЗ 26252 на 8 лет. Купон 12.5%. Выплата купонов 2 раза в год в апреле и октябре</t>
+  </si>
+  <si>
+    <t>RU000A10D4Y2</t>
+  </si>
+  <si>
+    <t>ОФЗ 26254 на 15 лет. Купон 13%. Выплата купонов 2 раза в год в апреле и октябре</t>
+  </si>
+  <si>
+    <t>RU000A10D533</t>
+  </si>
+  <si>
+    <t>ОФЗ 29008. Купонная доходность зависит от RUONIA за 6 месяцев +1.4%. Выплата 2 раза в год.</t>
+  </si>
+  <si>
+    <t>RU000A0JV4P3</t>
+  </si>
+  <si>
+    <t>ОФЗ 29008. Купонная доходность зависит от RUONIA за 6 месяцев +1.4%. Выплата 2 раза в год. Взял с рынка</t>
+  </si>
+  <si>
+    <t>ОФЗ 29025. Купонная доходность зависит от RUONIA за 6 месяцев + 0%. Выплата 4 раза в год: февраль, май, август, ноябрь</t>
+  </si>
+  <si>
+    <t>RU000A106Z61</t>
+  </si>
+  <si>
+    <t>Полипласт П02-БО-05 на 2 года. Первичное размещение под 25.5%. Выплата купона каждые 30 дней.</t>
+  </si>
+  <si>
+    <t>RU000A10BPN7</t>
+  </si>
+  <si>
+    <t>Облигации Село Зелёное серии 001Р-01 (RU000A10D4W6). На 1.5 года под КС+260 (при сборе заявок и КС=17% была вилка 19.6 - 20%) ежм без амортизации и оферты.</t>
+  </si>
+  <si>
+    <t>RU000A10D4W6</t>
+  </si>
+  <si>
+    <t>Облигации Сибур СЕРИИ 001P-08 в USD. На 5 лет под 6.65% (был диапазон 7-7.2%) каждые 30 дней, без амортизации и оферты. Размещение 03.09.25.</t>
+  </si>
+  <si>
+    <t>RU000A10CMR</t>
+  </si>
+  <si>
+    <t>Облигации ФосАгро БО-02-04 (RU000A10CZ68) USD под 7-7.25% (7% ФИНАЛ) ежм на 3 года (1106 дней) без оферты и амортизации</t>
+  </si>
+  <si>
+    <t>RU000A10CZ68</t>
+  </si>
+  <si>
+    <t>Группа ЛСР БО 001Р- 11. На 3 года под 16.25-17.25 ежм (ФИНАЛ 16%). Без оферты. Амортизация по 30% на 24 и 30 купонах.</t>
+  </si>
+  <si>
+    <t>Группа ЛСР БО 001Р-09. Купил с рынка по цене 96.98% с доходностью к погашению 18.54% с фикс купоном 14.75% ежм. Без амортизации.</t>
+  </si>
+  <si>
+    <t>RU000A1082X0</t>
+  </si>
+  <si>
+    <t>Облигации: Авто Финанс Банк, Б0-001P-17 (4802-17- 00170-B-001P) на 3 года под КС+215 ежм, без оферты и амортизации</t>
+  </si>
+  <si>
+    <t>RU000A10D9L8</t>
+  </si>
+  <si>
+    <t>ПАО ЮжУралзолото 001Р-04 USD (RU000A10B008). Купоны 10.6% ЕЖМ на 2 года</t>
+  </si>
+  <si>
+    <t>RU000A10B008</t>
+  </si>
+  <si>
+    <t>ПГК 003Р-02 (фикс) RU000A10DSL1 - Дата ДОПОЛНИТЕЛЬНОГО размещения: 05.02.26 Рейтинг: АА, прогноз «стабильный» (Эксперт РА) Купон ежемесячный: фикс ФИНАЛ= 15.95% Срок: 3,1 года фикс Амортизация: нет ОФЕРТА PUT: 29.03.29 Номинал: 1000 руб. !!! Внимание !!! ОФЕРТА PUT: 29.03.29 Можно ПРОДАТЬ после 05.02.29 с ЛДВ. Погашение: 16.11.30</t>
+  </si>
+  <si>
+    <t>РеСтор 001Р-02 на 2 года Купон: ФИНАЛ 18.85% (БЫЛО при сборе до 20%) - Выплаты: 12 раз в год - Рейтинг: A-(RU) от АКРА Со стабильным прогнозом - Амортизация: отсутствует - Оферта: отсутствует Погашение 28.11.27</t>
+  </si>
+  <si>
+    <t>RU000A10DMN0</t>
+  </si>
+  <si>
+    <t>Росагролизинг 002Р-04 под КС+2.2% ежм на 3 года без оферты и амортизации.</t>
+  </si>
+  <si>
+    <t>RU000A10CS91</t>
+  </si>
+  <si>
+    <t>Сбер 1P51 (фикс) Cбep-001P-SBER51 Купон: до 14,85% (YTM до 15,91%) Выплаты: 12 раз в год Срок: 2,5 лет (913 дней) до 16.06.28 Оферта: нет Амортизация: нет Выпуск для всех Кредитный рейтинг: ААА "стабильный" от АКРА (май 2025) и НКР (октябрь 2025).</t>
+  </si>
+  <si>
+    <t>RU000A109X37</t>
+  </si>
+  <si>
+    <t>RU000A10DS74</t>
+  </si>
+  <si>
+    <t>Сбербанк 001P- SberD3 RU000A109X37 Рейтинг: ААА ДИСКОНТНЫЕ ОБЛИГАЦИИ, купон 0% Срок: 3,7 лет Доходность: 15,5% Погашение 12.11.29 Приобретено с рынка 27.02.26 по цене 58.69, что даёт доходность 70.38% за 3.67 лет, или 15.44% годовой ставки. Кроме того, на доход должен действовать ЛДВ, то есть отсутствие налога</t>
+  </si>
+  <si>
+    <t>Селектел 001P-07R: • Рейтинг: АА- (Эксперт РА, прогноз «Стабильный») • Номинал: 1000Р Объем: 5 млрд рублей Срок обращения: 3 года • Купон: ФИНАЛ 15%, было не выше 16,60% годовых (УТМ не выше 17,92% годовых) • Периодичность выплат: ежемесячно • Амортизация: отсутствует Оферта: отсутствует Квал: не требуется • Сбор заявок: 27 февраля 2026 • Дата размещения: 04 марта 2026 года Погашение 16.02.29</t>
+  </si>
+  <si>
+    <t>RU000A10EEZ9</t>
+  </si>
+  <si>
+    <t>СелоЗел-001P-02 RU000A10DQ68 Рейтинг: А (НКР, прогноз «Стабильный») Купон: ФИНАЛ 17.25. Сбор заявок был с купоном до 18.00% (ежемесячный) Срок обращения: 2 года, до 25.11.27 Амортизация: нет Оферта: нет</t>
+  </si>
+  <si>
+    <t>RU000A10DQ68</t>
+  </si>
+  <si>
+    <t>Сибур 001Р-09 объем: $150 млн номинал: $100 купон: ФИНАЛ = 7.5% (было до 7,75) (ежемесячный) Годовых доходность: до 8,03% срок: 3 года (1110 дней= 06.03.29 ???) амортизация/оферта: нет рейтинг эмитента: AAA(RU) от АКРА, ruAAA от Эксперт РА доступно: всем сбор заявок: 18.02.26 Размещение 20.02.26</t>
+  </si>
+  <si>
+    <t>RU000A10ECK5</t>
+  </si>
+  <si>
+    <t>ТОМСКАЯ область. Томско6-34076 Рейтинг: BBB+ (Эксперт РА, прогноз «Стабильный») Купон: Финал 16.0% фикс, квартальный в марте, июне, сентябре и декабре. (Было КБД (3.2 года) +400 б.п. (фикс ориентировочно до 17.2%)) Срок обращения: 5 лет Объем: 5 млрд. Р Амортизация: да (16, 20 купоны по 50%) Оферта: нет Номинал: 1000 Р Сбор заявок 16 декабря 11:00-14:00 размещение 18 декабря 2025</t>
+  </si>
+  <si>
+    <t>RU000A10DWQ2</t>
+  </si>
+  <si>
+    <t>Томская область 34075 Ставка купона: КБД за 2.1 года + 5%. ФИНАЛ = 16.2%. Срок обращения: 3,1 года. Дюрация: 2,1 года Купон: 12 раз в год Рейтинг: BBB+ Амортизация: 40% – 25 купон, 60% – 37 купон Оферта: нет Дата размещения: 14.11.25</t>
+  </si>
+  <si>
+    <t>RU000A10DEN7</t>
+  </si>
+  <si>
+    <t>ФСК Россети-001P-19R FSKE001P19R RU000A10DM96 Погашение: через 2,8 года до 13.09.2028 Купон: КС +130 б.п. (При размещении КС+155) Выплаты: 12 раз в год Амортизация: Нет Оферта: Нет Рейтинг: AAA(RU) АКРА / ruAAA Эксперт РА</t>
+  </si>
+  <si>
+    <t>RU000A10DM96</t>
+  </si>
+  <si>
+    <t>Федеральная пассажирская компания АО «ФПК» 002P-01 RU000A10DYC8 Рейтинг: АА+, прогноз «стабильный» (НРА) Купон: ФИНАЛ 15.4 фикс. (КБД (2,5 года)+275 б.п., это до 15.9%), ежемесячный Срок: 2,5 года Объем: 30 млрд руб. Амортизация: нет Оферта: нет Номинал: 1000 руб. - Доступен неквал. инвесторам Дата размещения: 23 декабря</t>
+  </si>
+  <si>
+    <t>RU000A10DYC8</t>
+  </si>
+  <si>
+    <t>МКПАО Яндекс 001Р-03 - Купон: Ключевая ставка ЦБ + 1,45% (флоатер) - Выплаты: 12 раз в год (ежемесячно) - Погашение: Через 3 года - Рейтинг: ААА Амортизация: отсутствует - Оферта: отсутствует - Прием заявок: 13 ноября 2025, размещение 18 ноября</t>
+  </si>
+  <si>
+    <t>RU000A10DDR0</t>
+  </si>
+  <si>
+    <t>Эмитент: ООО «ИЛОН» Илон-001P-01 RU000A10EG44 - Купон: ФИНАЛ 17.7%. было Не выше 20,00% годовых (YTM до 21,94%). - Выплаты: Ежемесячно - Погашение: 2 года (720 дней) - Рейтинг: BBB+(RU), позитивный прогноз от AKPA (09.10.2025). - Амортизация: нет - Оферта: Отсутствует. - Объем выпуска: 1 млрд руб. - Прием заявок: До 03 марта 2026 г. Размещение 06.03.26 Дата погашения: 24.02.2028</t>
+  </si>
+  <si>
+    <t>RU000A10EG44</t>
+  </si>
+  <si>
+    <t>• АФК Система 002P-05 $RU000A10CU55 Рейтинг: АА- - Купон: ключевая ставка ЦБ+3,5% - Частота выплат: 12 раз в ГОД - КУПИЛ с рынка по цене цена: 994,5Р - Дата погашения: 16.09.2027</t>
+  </si>
+  <si>
+    <t>Рейтинг</t>
+  </si>
+  <si>
+    <t>АА</t>
+  </si>
+  <si>
+    <t>ВВ+</t>
+  </si>
+  <si>
+    <t>А+</t>
+  </si>
+  <si>
+    <t>ААА</t>
+  </si>
+  <si>
+    <t>ВВВ-</t>
+  </si>
+  <si>
+    <t>АА-</t>
+  </si>
+  <si>
+    <t>А</t>
+  </si>
+  <si>
+    <t>АА- Стабильный</t>
+  </si>
+  <si>
+    <t>АА Стабильный</t>
+  </si>
+  <si>
+    <t>ААА (АКРА, прогноз Стабильный)</t>
+  </si>
+  <si>
+    <t>АА- стабильный</t>
+  </si>
+  <si>
+    <t>ВВВ</t>
+  </si>
+  <si>
+    <t>А Стабильный</t>
+  </si>
+  <si>
+    <t>АА-, А+</t>
+  </si>
+  <si>
+    <t>А- Стабильный</t>
+  </si>
+  <si>
+    <t>АА- негативный</t>
+  </si>
+  <si>
+    <t>А- негативный</t>
+  </si>
+  <si>
+    <t>А-</t>
+  </si>
+  <si>
+    <t>AAA Стабильный</t>
+  </si>
+  <si>
+    <t>ВВ Стабильный</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>ВВВ+</t>
+  </si>
+  <si>
+    <t>АА+</t>
+  </si>
+  <si>
+    <t>BBB+</t>
+  </si>
+  <si>
+    <t>Кол-во обл</t>
+  </si>
+  <si>
+    <t>Средняя цена</t>
+  </si>
+  <si>
+    <t>ТКД</t>
+  </si>
+  <si>
+    <t>Дата оферты</t>
+  </si>
+  <si>
+    <t>29 февр. 2028 г.</t>
+  </si>
+  <si>
+    <t>29 мар. 2029 г.</t>
+  </si>
+  <si>
+    <t>27 авг. 2028 г.</t>
+  </si>
+  <si>
+    <t>10 февр. 2028 г.</t>
+  </si>
+  <si>
+    <t>24 дек. 2027 г.</t>
+  </si>
+  <si>
+    <t>16 мар. 2027 г.</t>
+  </si>
+  <si>
+    <t>Спекуляции</t>
+  </si>
+  <si>
+    <t>да</t>
   </si>
 </sst>
 </file>
@@ -172,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -194,6 +812,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,14 +1142,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586A65F8-F944-4B4D-A5BF-3F3B83B05D40}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,140 +1159,2908 @@
       <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="10">
+        <v>100</v>
+      </c>
+      <c r="F2" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G2" s="4">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" ht="79.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C3" s="3">
         <v>103.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="D3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="11">
+        <v>136</v>
+      </c>
+      <c r="F3" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" s="10">
+        <v>900</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="4">
+        <v>17</v>
+      </c>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="11">
+        <v>400</v>
+      </c>
+      <c r="F5" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="H5" s="9"/>
+    </row>
+    <row r="6" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E6" s="11">
+        <v>30</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1000.6</v>
+      </c>
+      <c r="G6" s="2">
+        <v>16.63</v>
+      </c>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="10">
+        <v>100</v>
+      </c>
+      <c r="F7" s="10">
+        <v>998.2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>16.73</v>
+      </c>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="11">
+        <v>203</v>
+      </c>
+      <c r="F8" s="11">
+        <v>998.7</v>
+      </c>
+      <c r="G8" s="2">
+        <v>15.971</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C9" s="5">
         <v>103.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="D9" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="10">
+        <v>300</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="4">
+        <v>24.5</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="11">
+        <v>100</v>
+      </c>
+      <c r="F10" s="11">
+        <v>993.7</v>
+      </c>
+      <c r="G10" s="2">
+        <v>19.12</v>
+      </c>
+      <c r="H10" s="9"/>
+    </row>
+    <row r="11" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C11" s="5">
         <v>103.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="57" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="D11" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="10">
+        <v>149</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="4">
+        <v>20</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="11">
+        <v>220</v>
+      </c>
+      <c r="F12" s="11">
+        <v>1691.2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>244</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1195.2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" s="10">
+        <v>200</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="4">
+        <v>15.15</v>
+      </c>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E15" s="11">
+        <v>300</v>
+      </c>
+      <c r="F15" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="2">
+        <v>15.15</v>
+      </c>
+      <c r="H15" s="9"/>
+    </row>
+    <row r="16" spans="1:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="10">
+        <v>500</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G16" s="4">
+        <v>14.7</v>
+      </c>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E17" s="11">
+        <v>300</v>
+      </c>
+      <c r="F17" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E18" s="10">
+        <v>200</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G18" s="4">
+        <v>22.25</v>
+      </c>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="11">
+        <v>200</v>
+      </c>
+      <c r="F19" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G19" s="2">
+        <v>22.25</v>
+      </c>
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="10">
+        <v>29</v>
+      </c>
+      <c r="F20" s="10">
+        <v>982.03</v>
+      </c>
+      <c r="G20" s="4">
+        <v>17.311</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="11">
+        <v>300</v>
+      </c>
+      <c r="F21" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="2">
+        <v>17</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="10">
+        <v>300</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="4">
+        <v>17</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" s="11">
+        <v>500</v>
+      </c>
+      <c r="F23" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="2">
+        <v>17</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" s="10">
+        <v>80</v>
+      </c>
+      <c r="F24" s="10">
+        <v>834</v>
+      </c>
+      <c r="G24" s="4">
+        <v>18.585000000000001</v>
+      </c>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" s="11">
+        <v>160</v>
+      </c>
+      <c r="F25" s="11">
+        <v>834</v>
+      </c>
+      <c r="G25" s="2">
+        <v>18.585000000000001</v>
+      </c>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10">
+        <v>80153.38</v>
+      </c>
+      <c r="G26" s="4">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" s="11">
+        <v>5</v>
+      </c>
+      <c r="F27" s="11">
+        <v>83606.899999999994</v>
+      </c>
+      <c r="G27" s="2">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="10">
+        <v>50</v>
+      </c>
+      <c r="F28" s="10">
+        <v>988.1</v>
+      </c>
+      <c r="G28" s="4">
+        <v>17.407</v>
+      </c>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="11">
+        <v>417</v>
+      </c>
+      <c r="F29" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G29" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="10">
+        <v>300</v>
+      </c>
+      <c r="F30" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G30" s="4">
+        <v>20</v>
+      </c>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E31" s="11">
+        <v>23</v>
+      </c>
+      <c r="F31" s="11">
+        <v>7662.01</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1.24</v>
+      </c>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" s="10">
+        <v>500</v>
+      </c>
+      <c r="F32" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G32" s="4">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E33" s="11">
+        <v>9</v>
+      </c>
+      <c r="F33" s="11">
+        <v>78839</v>
+      </c>
+      <c r="G33" s="2">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E34" s="10">
+        <v>500</v>
+      </c>
+      <c r="F34" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G34" s="4">
+        <v>17</v>
+      </c>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35" s="11">
+        <v>400</v>
+      </c>
+      <c r="F35" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G35" s="2">
+        <v>17</v>
+      </c>
+      <c r="H35" s="9"/>
+    </row>
+    <row r="36" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36" s="10">
+        <v>34</v>
+      </c>
+      <c r="F36" s="10">
+        <v>1008.75</v>
+      </c>
+      <c r="G36" s="4">
+        <v>17.347999999999999</v>
+      </c>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C37" s="3">
         <v>104.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="D37" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E37" s="11">
+        <v>330</v>
+      </c>
+      <c r="F37" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G37" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E38" s="10">
+        <v>22</v>
+      </c>
+      <c r="F38" s="10">
+        <v>998</v>
+      </c>
+      <c r="G38" s="4">
+        <v>16.032</v>
+      </c>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E39" s="11">
+        <v>200</v>
+      </c>
+      <c r="F39" s="11">
+        <v>996.57500000000005</v>
+      </c>
+      <c r="G39" s="2">
+        <v>17.209</v>
+      </c>
+      <c r="H39" s="9"/>
+    </row>
+    <row r="40" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" s="10">
+        <v>200</v>
+      </c>
+      <c r="F40" s="10">
+        <v>996.9</v>
+      </c>
+      <c r="G40" s="4">
+        <v>17.202999999999999</v>
+      </c>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="11">
+        <v>264</v>
+      </c>
+      <c r="F41" s="11">
+        <v>164.72</v>
+      </c>
+      <c r="G41" s="2">
+        <v>94.099000000000004</v>
+      </c>
+      <c r="H41" s="9"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="10">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="F42" s="10">
+        <v>159.83000000000001</v>
+      </c>
+      <c r="G42" s="4">
+        <v>96.977999999999994</v>
+      </c>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="11">
+        <v>498</v>
+      </c>
+      <c r="F43" s="11">
+        <v>165.55</v>
+      </c>
+      <c r="G43" s="2">
+        <v>93.626999999999995</v>
+      </c>
+      <c r="H43" s="9"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="10">
+        <v>24</v>
+      </c>
+      <c r="F44" s="10">
+        <v>153.31</v>
+      </c>
+      <c r="G44" s="4">
+        <v>104.364</v>
+      </c>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="11">
+        <v>336</v>
+      </c>
+      <c r="F45" s="11">
+        <v>153.13</v>
+      </c>
+      <c r="G45" s="2">
+        <v>104.486</v>
+      </c>
+      <c r="H45" s="9"/>
+    </row>
+    <row r="46" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E46" s="11">
+        <v>100</v>
+      </c>
+      <c r="F46" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G46" s="2">
+        <v>17</v>
+      </c>
+      <c r="H46" s="9"/>
+    </row>
+    <row r="47" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" s="10">
+        <v>23</v>
+      </c>
+      <c r="F47" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G47" s="4">
+        <v>15.75</v>
+      </c>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="11">
+        <v>1</v>
+      </c>
+      <c r="F48" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G48" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" s="10">
+        <v>31</v>
+      </c>
+      <c r="F49" s="10">
+        <v>1001.2</v>
+      </c>
+      <c r="G49" s="4">
+        <v>18.378</v>
+      </c>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E50" s="11">
+        <v>170</v>
+      </c>
+      <c r="F50" s="11">
+        <v>1001.1</v>
+      </c>
+      <c r="G50" s="2">
+        <v>18.38</v>
+      </c>
+      <c r="H50" s="9"/>
+    </row>
+    <row r="51" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="10">
+        <v>180</v>
+      </c>
+      <c r="F51" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G51" s="4">
+        <v>17.3</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E52" s="11">
+        <v>10</v>
+      </c>
+      <c r="F52" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G52" s="2">
+        <v>17</v>
+      </c>
+      <c r="H52" s="9"/>
+    </row>
+    <row r="53" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" s="10">
+        <v>200</v>
+      </c>
+      <c r="F53" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G53" s="4">
+        <v>15.25</v>
+      </c>
+      <c r="H53" s="8"/>
+    </row>
+    <row r="54" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="9"/>
+      <c r="D54" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" s="11">
+        <v>400</v>
+      </c>
+      <c r="F54" s="11">
+        <v>896.4</v>
+      </c>
+      <c r="G54" s="2">
+        <v>13.666</v>
+      </c>
+      <c r="H54" s="9"/>
+    </row>
+    <row r="55" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E55" s="10">
+        <v>300</v>
+      </c>
+      <c r="F55" s="10">
+        <v>878.6</v>
+      </c>
+      <c r="G55" s="4">
+        <v>13.657999999999999</v>
+      </c>
+      <c r="H55" s="8"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" s="11">
+        <v>733</v>
+      </c>
+      <c r="F56" s="11">
+        <v>928.32</v>
+      </c>
+      <c r="G56" s="2">
+        <v>14.004</v>
+      </c>
+      <c r="H56" s="9"/>
+    </row>
+    <row r="57" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C57" s="8"/>
+      <c r="D57" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E57" s="10">
+        <v>50</v>
+      </c>
+      <c r="F57" s="10">
+        <v>1000.2</v>
+      </c>
+      <c r="G57" s="4">
+        <v>16.896999999999998</v>
+      </c>
+      <c r="H57" s="8"/>
+    </row>
+    <row r="58" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E58" s="11">
+        <v>100</v>
+      </c>
+      <c r="F58" s="11">
+        <v>999.2</v>
+      </c>
+      <c r="G58" s="2">
+        <v>15.412000000000001</v>
+      </c>
+      <c r="H58" s="9"/>
+    </row>
+    <row r="59" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" s="8"/>
+      <c r="D59" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" s="10">
+        <v>33</v>
+      </c>
+      <c r="F59" s="10">
+        <v>8126.9</v>
+      </c>
+      <c r="G59" s="4">
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="H59" s="8"/>
+    </row>
+    <row r="60" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E60" s="11">
+        <v>8</v>
+      </c>
+      <c r="F60" s="11">
+        <v>7848.39</v>
+      </c>
+      <c r="G60" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="H60" s="9"/>
+    </row>
+    <row r="61" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C61" s="8"/>
+      <c r="D61" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E61" s="10">
+        <v>6</v>
+      </c>
+      <c r="F61" s="10">
+        <v>7848</v>
+      </c>
+      <c r="G61" s="4">
+        <v>1.65</v>
+      </c>
+      <c r="H61" s="8"/>
+    </row>
+    <row r="62" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="9"/>
+      <c r="D62" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E62" s="11">
+        <v>35</v>
+      </c>
+      <c r="F62" s="11">
+        <v>8010.45</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1.4039999999999999</v>
+      </c>
+      <c r="H62" s="9"/>
+    </row>
+    <row r="63" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E63" s="10">
+        <v>148</v>
+      </c>
+      <c r="F63" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G63" s="4">
+        <v>20.25</v>
+      </c>
+      <c r="H63" s="8"/>
+    </row>
+    <row r="64" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C64" s="9"/>
+      <c r="D64" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E64" s="11">
+        <v>223</v>
+      </c>
+      <c r="F64" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G64" s="2">
+        <v>20.25</v>
+      </c>
+      <c r="H64" s="9"/>
+    </row>
+    <row r="65" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" s="8"/>
+      <c r="D65" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" s="10">
+        <v>100</v>
+      </c>
+      <c r="F65" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G65" s="4">
+        <v>22.75</v>
+      </c>
+      <c r="H65" s="8"/>
+    </row>
+    <row r="66" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" s="9"/>
+      <c r="D66" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E66" s="11">
+        <v>300</v>
+      </c>
+      <c r="F66" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G66" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="H66" s="9"/>
+    </row>
+    <row r="67" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" s="8"/>
+      <c r="D67" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" s="10">
+        <v>100</v>
+      </c>
+      <c r="F67" s="10">
+        <v>988</v>
+      </c>
+      <c r="G67" s="4">
+        <v>14.523999999999999</v>
+      </c>
+      <c r="H67" s="8"/>
+    </row>
+    <row r="68" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="9"/>
+      <c r="D68" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E68" s="11">
+        <v>222</v>
+      </c>
+      <c r="F68" s="11">
+        <v>991.9</v>
+      </c>
+      <c r="G68" s="2">
+        <v>14.467000000000001</v>
+      </c>
+      <c r="H68" s="9"/>
+    </row>
+    <row r="69" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C69" s="8"/>
+      <c r="D69" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E69" s="10">
+        <v>150</v>
+      </c>
+      <c r="F69" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G69" s="4">
+        <v>14.7</v>
+      </c>
+      <c r="H69" s="8"/>
+    </row>
+    <row r="70" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" s="9"/>
+      <c r="D70" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" s="11">
+        <v>500</v>
+      </c>
+      <c r="F70" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G70" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="H70" s="9"/>
+    </row>
+    <row r="71" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C71" s="8"/>
+      <c r="D71" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E71" s="10">
+        <v>500</v>
+      </c>
+      <c r="F71" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G71" s="4">
+        <v>15.1</v>
+      </c>
+      <c r="H71" s="8"/>
+    </row>
+    <row r="72" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" s="9"/>
+      <c r="D72" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" s="11">
+        <v>700</v>
+      </c>
+      <c r="F72" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G72" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="H72" s="9"/>
+    </row>
+    <row r="73" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C73" s="8"/>
+      <c r="D73" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E73" s="10">
+        <v>3000</v>
+      </c>
+      <c r="F73" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G73" s="4">
+        <v>8.35</v>
+      </c>
+      <c r="H73" s="8"/>
+    </row>
+    <row r="74" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C74" s="3">
         <v>101</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="D74" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E74" s="11">
+        <v>200</v>
+      </c>
+      <c r="F74" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G74" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="H74" s="9"/>
+    </row>
+    <row r="75" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C75" s="5">
         <v>101</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="D75" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E75" s="10">
+        <v>200</v>
+      </c>
+      <c r="F75" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G75" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="H75" s="8"/>
+    </row>
+    <row r="76" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C76" s="9"/>
+      <c r="D76" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" s="11">
+        <v>200</v>
+      </c>
+      <c r="F76" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G76" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="H76" s="9"/>
+    </row>
+    <row r="77" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" s="8"/>
+      <c r="D77" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E77" s="10">
+        <v>11</v>
+      </c>
+      <c r="F77" s="10">
+        <v>8307.18</v>
+      </c>
+      <c r="G77" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="H77" s="8"/>
+    </row>
+    <row r="78" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E78" s="11">
+        <v>169</v>
+      </c>
+      <c r="F78" s="11">
+        <v>8306.43</v>
+      </c>
+      <c r="G78" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="H78" s="9"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B79" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C79" s="5">
         <v>112</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="D79" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E79" s="10">
+        <v>26</v>
+      </c>
+      <c r="F79" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G79" s="4">
+        <v>22</v>
+      </c>
+      <c r="H79" s="8"/>
+    </row>
+    <row r="80" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E80" s="11">
+        <v>119</v>
+      </c>
+      <c r="F80" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G80" s="2">
+        <v>16</v>
+      </c>
+      <c r="H80" s="9"/>
+    </row>
+    <row r="81" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C81" s="8"/>
+      <c r="D81" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="10">
+        <v>200</v>
+      </c>
+      <c r="F81" s="10">
+        <v>992.5</v>
+      </c>
+      <c r="G81" s="4">
+        <v>18.388000000000002</v>
+      </c>
+      <c r="H81" s="8"/>
+    </row>
+    <row r="82" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E82" s="11">
+        <v>250</v>
+      </c>
+      <c r="F82" s="11">
+        <v>998.98</v>
+      </c>
+      <c r="G82" s="2">
+        <v>18.268999999999998</v>
+      </c>
+      <c r="H82" s="9"/>
+    </row>
+    <row r="83" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C83" s="8"/>
+      <c r="D83" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E83" s="10">
+        <v>384</v>
+      </c>
+      <c r="F83" s="10">
+        <v>1001.9</v>
+      </c>
+      <c r="G83" s="4">
+        <v>18.465</v>
+      </c>
+      <c r="H83" s="8"/>
+    </row>
+    <row r="84" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E84" s="11">
+        <v>235</v>
+      </c>
+      <c r="F84" s="11">
+        <v>1000.7</v>
+      </c>
+      <c r="G84" s="2">
+        <v>18.486999999999998</v>
+      </c>
+      <c r="H84" s="9"/>
+    </row>
+    <row r="85" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C85" s="8"/>
+      <c r="D85" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E85" s="10">
+        <v>508</v>
+      </c>
+      <c r="F85" s="10">
+        <v>1004.5</v>
+      </c>
+      <c r="G85" s="4">
+        <v>18.417000000000002</v>
+      </c>
+      <c r="H85" s="8"/>
+    </row>
+    <row r="86" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E86" s="11">
+        <v>200</v>
+      </c>
+      <c r="F86" s="11">
+        <v>997.8</v>
+      </c>
+      <c r="G86" s="2">
+        <v>17.036999999999999</v>
+      </c>
+      <c r="H86" s="9"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C87" s="8"/>
+      <c r="D87" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E87" s="10">
+        <v>50</v>
+      </c>
+      <c r="F87" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G87" s="4">
+        <v>7.95</v>
+      </c>
+      <c r="H87" s="8"/>
+    </row>
+    <row r="88" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E88" s="11">
+        <v>20</v>
+      </c>
+      <c r="F88" s="11">
+        <v>895.32</v>
+      </c>
+      <c r="G88" s="2">
+        <v>13.682</v>
+      </c>
+      <c r="H88" s="9"/>
+    </row>
+    <row r="89" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="8"/>
+      <c r="D89" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E89" s="10">
+        <v>315</v>
+      </c>
+      <c r="F89" s="10">
+        <v>901.05</v>
+      </c>
+      <c r="G89" s="4">
+        <v>13.595000000000001</v>
+      </c>
+      <c r="H89" s="8"/>
+    </row>
+    <row r="90" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E90" s="11">
+        <v>2600</v>
+      </c>
+      <c r="F90" s="11">
+        <v>865.78</v>
+      </c>
+      <c r="G90" s="2">
+        <v>14.148999999999999</v>
+      </c>
+      <c r="H90" s="9"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C91" s="8"/>
+      <c r="D91" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E91" s="10">
+        <v>1000</v>
+      </c>
+      <c r="F91" s="10">
+        <v>916.62</v>
+      </c>
+      <c r="G91" s="4">
+        <v>13.637</v>
+      </c>
+      <c r="H91" s="8"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E92" s="11">
+        <v>1402</v>
+      </c>
+      <c r="F92" s="11">
+        <v>938.29</v>
+      </c>
+      <c r="G92" s="2">
+        <v>13.855</v>
+      </c>
+      <c r="H92" s="9"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C93" s="8"/>
+      <c r="D93" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E93" s="10">
+        <v>109</v>
+      </c>
+      <c r="F93" s="10">
+        <v>900.3</v>
+      </c>
+      <c r="G93" s="4">
+        <v>14.44</v>
+      </c>
+      <c r="H93" s="8"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C94" s="9"/>
+      <c r="D94" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E94" s="11">
+        <v>151</v>
+      </c>
+      <c r="F94" s="11">
+        <v>920.87</v>
+      </c>
+      <c r="G94" s="2">
+        <v>14.117000000000001</v>
+      </c>
+      <c r="H94" s="9"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C95" s="8"/>
+      <c r="D95" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E95" s="10">
+        <v>267</v>
+      </c>
+      <c r="F95" s="10">
+        <v>915.39</v>
+      </c>
+      <c r="G95" s="4">
+        <v>14.202</v>
+      </c>
+      <c r="H95" s="8"/>
+    </row>
+    <row r="96" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E96" s="11">
+        <v>200</v>
+      </c>
+      <c r="F96" s="11">
+        <v>1048.93</v>
+      </c>
+      <c r="G96" s="2">
+        <v>19.677</v>
+      </c>
+      <c r="H96" s="9"/>
+    </row>
+    <row r="97" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C97" s="8"/>
+      <c r="D97" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E97" s="10">
+        <v>603</v>
+      </c>
+      <c r="F97" s="10">
+        <v>1045.19</v>
+      </c>
+      <c r="G97" s="4">
+        <v>19.748000000000001</v>
+      </c>
+      <c r="H97" s="8"/>
+    </row>
+    <row r="98" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E98" s="11">
+        <v>700</v>
+      </c>
+      <c r="F98" s="11">
+        <v>1046.02</v>
+      </c>
+      <c r="G98" s="2">
+        <v>19.731999999999999</v>
+      </c>
+      <c r="H98" s="9"/>
+    </row>
+    <row r="99" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C99" s="8"/>
+      <c r="D99" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E99" s="10">
+        <v>100</v>
+      </c>
+      <c r="F99" s="10">
+        <v>945.52</v>
+      </c>
+      <c r="G99" s="4">
+        <v>0</v>
+      </c>
+      <c r="H99" s="8"/>
+    </row>
+    <row r="100" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C100" s="9"/>
+      <c r="D100" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E100" s="11">
+        <v>500</v>
+      </c>
+      <c r="F100" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G100" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="H100" s="9"/>
+    </row>
+    <row r="101" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C101" s="8"/>
+      <c r="D101" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E101" s="10">
+        <v>10</v>
+      </c>
+      <c r="F101" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G101" s="4">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="H101" s="8"/>
+    </row>
+    <row r="102" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C102" s="9"/>
+      <c r="D102" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E102" s="11">
+        <v>17</v>
+      </c>
+      <c r="F102" s="11">
+        <v>8059.47</v>
+      </c>
+      <c r="G102" s="2">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="H102" s="9"/>
+    </row>
+    <row r="103" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C103" s="8"/>
+      <c r="D103" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103" s="10">
+        <v>6</v>
+      </c>
+      <c r="F103" s="10">
+        <v>81496.7</v>
+      </c>
+      <c r="G103" s="4">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="H103" s="8"/>
+    </row>
+    <row r="104" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B104" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C104" s="3">
         <v>104.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="D104" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E104" s="11">
+        <v>48</v>
+      </c>
+      <c r="F104" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G104" s="2">
+        <v>22</v>
+      </c>
+      <c r="H104" s="9"/>
+    </row>
+    <row r="105" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C105" s="8"/>
+      <c r="D105" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E105" s="10">
+        <v>159</v>
+      </c>
+      <c r="F105" s="10">
+        <v>996.06</v>
+      </c>
+      <c r="G105" s="4">
+        <v>16.062999999999999</v>
+      </c>
+      <c r="H105" s="8"/>
+    </row>
+    <row r="106" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C106" s="9"/>
+      <c r="D106" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E106" s="11">
+        <v>100</v>
+      </c>
+      <c r="F106" s="11">
+        <v>969.8</v>
+      </c>
+      <c r="G106" s="2">
+        <v>15.209</v>
+      </c>
+      <c r="H106" s="9"/>
+    </row>
+    <row r="107" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C107" s="8"/>
+      <c r="D107" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E107" s="10">
+        <v>254</v>
+      </c>
+      <c r="F107" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G107" s="4">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="H107" s="8"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C108" s="9"/>
+      <c r="D108" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E108" s="11">
+        <v>15</v>
+      </c>
+      <c r="F108" s="11">
+        <v>8093.93</v>
+      </c>
+      <c r="G108" s="2">
+        <v>1.31</v>
+      </c>
+      <c r="H108" s="9"/>
+    </row>
+    <row r="109" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C109" s="8"/>
+      <c r="D109" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E109" s="10">
+        <v>200</v>
+      </c>
+      <c r="F109" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G109" s="4">
+        <v>15.95</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C110" s="9"/>
+      <c r="D110" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E110" s="11">
+        <v>95</v>
+      </c>
+      <c r="F110" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G110" s="2">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="H110" s="9"/>
+    </row>
+    <row r="111" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C111" s="8"/>
+      <c r="D111" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E111" s="10">
+        <v>165</v>
+      </c>
+      <c r="F111" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G111" s="4">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="H111" s="8"/>
+    </row>
+    <row r="112" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C112" s="9"/>
+      <c r="D112" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E112" s="11">
+        <v>100</v>
+      </c>
+      <c r="F112" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G112" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="H112" s="9"/>
+    </row>
+    <row r="113" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A113" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B113" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C113" s="7">
+        <v>104.5</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E113" s="12">
+        <v>6</v>
+      </c>
+      <c r="F113" s="12">
+        <v>1000</v>
+      </c>
+      <c r="G113" s="6">
+        <v>27</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C114" s="9"/>
+      <c r="D114" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E114" s="11">
+        <v>300</v>
+      </c>
+      <c r="F114" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G114" s="2">
+        <v>14.85</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C115" s="8"/>
+      <c r="D115" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E115" s="10">
+        <v>350</v>
+      </c>
+      <c r="F115" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G115" s="4">
+        <v>14.85</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C116" s="9"/>
+      <c r="D116" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E116" s="11">
+        <v>200</v>
+      </c>
+      <c r="F116" s="11">
+        <v>586.9</v>
+      </c>
+      <c r="G116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C117" s="8"/>
+      <c r="D117" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E117" s="10">
+        <v>100</v>
+      </c>
+      <c r="F117" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G117" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" s="3">
         <v>103.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="D118" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E118" s="11">
+        <v>100</v>
+      </c>
+      <c r="F118" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G118" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C119" s="5">
         <v>103.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5">
-        <v>103.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="57" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="D119" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E119" s="10">
+        <v>200</v>
+      </c>
+      <c r="F119" s="10">
+        <v>1003.68</v>
+      </c>
+      <c r="G119" s="4">
+        <v>19.927</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C120" s="9"/>
+      <c r="D120" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E120" s="11">
+        <v>210</v>
+      </c>
+      <c r="F120" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G120" s="2">
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C121" s="8"/>
+      <c r="D121" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E121" s="10">
+        <v>210</v>
+      </c>
+      <c r="F121" s="10">
+        <v>995</v>
+      </c>
+      <c r="G121" s="4">
+        <v>17.337</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C122" s="9"/>
+      <c r="D122" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E122" s="11">
+        <v>3</v>
+      </c>
+      <c r="F122" s="11">
+        <v>7664.05</v>
+      </c>
+      <c r="G122" s="2">
+        <v>0.97899999999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C123" s="8"/>
+      <c r="D123" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E123" s="10">
+        <v>10</v>
+      </c>
+      <c r="F123" s="10">
+        <v>7664.05</v>
+      </c>
+      <c r="G123" s="4">
+        <v>0.97899999999999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B124" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C124" s="5">
         <v>107</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E124" s="10">
+        <v>200</v>
+      </c>
+      <c r="F124" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G124" s="4">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C125" s="9"/>
+      <c r="D125" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E125" s="11">
+        <v>52</v>
+      </c>
+      <c r="F125" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G125" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C126" s="9"/>
+      <c r="D126" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E126" s="11">
+        <v>50</v>
+      </c>
+      <c r="F126" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G126" s="2">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C127" s="8"/>
+      <c r="D127" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E127" s="10">
+        <v>200</v>
+      </c>
+      <c r="F127" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G127" s="4">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C128" s="9"/>
+      <c r="D128" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E128" s="11">
+        <v>400</v>
+      </c>
+      <c r="F128" s="11">
+        <v>995</v>
+      </c>
+      <c r="G128" s="2">
+        <v>15.477</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C129" s="8"/>
+      <c r="D129" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E129" s="10">
+        <v>200</v>
+      </c>
+      <c r="F129" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G129" s="4">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="57" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C130" s="9"/>
+      <c r="D130" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E130" s="11">
+        <v>86</v>
+      </c>
+      <c r="F130" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G130" s="2">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C131" s="8"/>
+      <c r="D131" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E131" s="10">
+        <v>100</v>
+      </c>
+      <c r="F131" s="10">
+        <v>994.5</v>
+      </c>
+      <c r="G131" s="4">
+        <v>19.105</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Bonds/bonds.xlsx
+++ b/Bonds/bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ilya\Documents\GitHub\projects\Bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9ADF0EB-355E-4B09-8B7A-DCC626ECD787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FAA236-70F9-43D1-8568-7CAD7D0FA084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C1DB8464-260E-4338-9640-726B3E736107}"/>
   </bookViews>
@@ -222,9 +222,6 @@
     <t>Газпром капитал БО-003Р-06 на 2 года под 17.5-18.5% (финал=КС+1.4) ежм без оферты и амортизации</t>
   </si>
   <si>
-    <t>RUO00A10D2Q2</t>
-  </si>
-  <si>
     <t>Газпром нефть 005P-01R USD RU000A10D483 под 5.5-7.75% (ФИНАЛ 7.5%) ежм на 3.5 года без оферты и амортизации. Номинал 1000 USD</t>
   </si>
   <si>
@@ -408,9 +405,6 @@
     <t>Облигации ВТБ Лизинг 001Р-МБ-04 АА RU000VTBL1P4 на 3 года. Первичное размещение под 16.5%. Выплата каждые 30 дней. Амортизация каждые 3 мес по 8%, при завершении ещё 12%. Оферты нет. Размещение 16.12.25</t>
   </si>
   <si>
-    <t>RU000VTBL1P4</t>
-  </si>
-  <si>
     <t>Облигации ГМК Норникель БО-001P-14-USD под 6.5-7% (финал 6.4%) ежм на 4 года без оферты и амортизации.</t>
   </si>
   <si>
@@ -715,6 +709,12 @@
   </si>
   <si>
     <t>да</t>
+  </si>
+  <si>
+    <t>RU000A10DTG9</t>
+  </si>
+  <si>
+    <t>RU000A10D2Q2</t>
   </si>
 </sst>
 </file>
@@ -1160,22 +1160,22 @@
         <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E2" s="10">
         <v>100</v>
@@ -1211,7 +1211,7 @@
         <v>103.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E3" s="11">
         <v>136</v>
@@ -1223,10 +1223,10 @@
         <v>23.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E4" s="10">
         <v>900</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E5" s="11">
         <v>400</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E6" s="11">
         <v>30</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E7" s="10">
         <v>100</v>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E8" s="11">
         <v>203</v>
@@ -1338,7 +1338,7 @@
         <v>15.971</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
@@ -1352,7 +1352,7 @@
         <v>103.5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E9" s="10">
         <v>300</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="H9" s="8"/>
       <c r="I9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E10" s="11">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>103.5</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E11" s="10">
         <v>149</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H11" s="8"/>
       <c r="I11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E14" s="10">
         <v>200</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E15" s="11">
         <v>300</v>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E16" s="10">
         <v>500</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E17" s="11">
         <v>300</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E18" s="10">
         <v>200</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E19" s="11">
         <v>200</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E20" s="10">
         <v>29</v>
@@ -1610,7 +1610,7 @@
         <v>17.311</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E21" s="11">
         <v>300</v>
@@ -1634,7 +1634,7 @@
         <v>17</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E22" s="10">
         <v>300</v>
@@ -1658,7 +1658,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E23" s="11">
         <v>500</v>
@@ -1682,7 +1682,7 @@
         <v>17</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E24" s="10">
         <v>80</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E25" s="11">
         <v>160</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E26" s="10">
         <v>1</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E27" s="11">
         <v>5</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E28" s="10">
         <v>50</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E29" s="11">
         <v>417</v>
@@ -1816,7 +1816,7 @@
         <v>16.5</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E30" s="10">
         <v>300</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E31" s="11">
         <v>23</v>
@@ -1868,11 +1868,11 @@
         <v>64</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>65</v>
+        <v>229</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E32" s="10">
         <v>500</v>
@@ -1887,14 +1887,14 @@
     </row>
     <row r="33" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E33" s="11">
         <v>9</v>
@@ -1909,14 +1909,14 @@
     </row>
     <row r="34" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E34" s="10">
         <v>500</v>
@@ -1931,14 +1931,14 @@
     </row>
     <row r="35" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E35" s="11">
         <v>400</v>
@@ -1953,14 +1953,14 @@
     </row>
     <row r="36" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E36" s="10">
         <v>34</v>
@@ -1984,7 +1984,7 @@
         <v>104.5</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E37" s="11">
         <v>330</v>
@@ -1999,14 +1999,14 @@
     </row>
     <row r="38" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E38" s="10">
         <v>22</v>
@@ -2021,14 +2021,14 @@
     </row>
     <row r="39" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E39" s="11">
         <v>200</v>
@@ -2043,14 +2043,14 @@
     </row>
     <row r="40" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E40" s="10">
         <v>200</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -2125,10 +2125,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -2165,14 +2165,14 @@
     </row>
     <row r="46" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E46" s="11">
         <v>100</v>
@@ -2187,14 +2187,14 @@
     </row>
     <row r="47" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E47" s="10">
         <v>23</v>
@@ -2209,14 +2209,14 @@
     </row>
     <row r="48" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E48" s="11">
         <v>1</v>
@@ -2231,14 +2231,14 @@
     </row>
     <row r="49" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E49" s="10">
         <v>31</v>
@@ -2253,14 +2253,14 @@
     </row>
     <row r="50" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E50" s="11">
         <v>170</v>
@@ -2275,14 +2275,14 @@
     </row>
     <row r="51" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E51" s="10">
         <v>180</v>
@@ -2294,19 +2294,19 @@
         <v>17.3</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E52" s="11">
         <v>10</v>
@@ -2321,14 +2321,14 @@
     </row>
     <row r="53" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E53" s="10">
         <v>200</v>
@@ -2343,14 +2343,14 @@
     </row>
     <row r="54" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E54" s="11">
         <v>400</v>
@@ -2365,14 +2365,14 @@
     </row>
     <row r="55" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E55" s="10">
         <v>300</v>
@@ -2387,14 +2387,14 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E56" s="11">
         <v>733</v>
@@ -2409,14 +2409,14 @@
     </row>
     <row r="57" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E57" s="10">
         <v>50</v>
@@ -2431,14 +2431,14 @@
     </row>
     <row r="58" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E58" s="11">
         <v>100</v>
@@ -2453,14 +2453,14 @@
     </row>
     <row r="59" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E59" s="10">
         <v>33</v>
@@ -2475,14 +2475,14 @@
     </row>
     <row r="60" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E60" s="11">
         <v>8</v>
@@ -2497,14 +2497,14 @@
     </row>
     <row r="61" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E61" s="10">
         <v>6</v>
@@ -2519,14 +2519,14 @@
     </row>
     <row r="62" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E62" s="11">
         <v>35</v>
@@ -2541,14 +2541,14 @@
     </row>
     <row r="63" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E63" s="10">
         <v>148</v>
@@ -2563,14 +2563,14 @@
     </row>
     <row r="64" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E64" s="11">
         <v>223</v>
@@ -2585,14 +2585,14 @@
     </row>
     <row r="65" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E65" s="10">
         <v>100</v>
@@ -2607,14 +2607,14 @@
     </row>
     <row r="66" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E66" s="11">
         <v>300</v>
@@ -2629,14 +2629,14 @@
     </row>
     <row r="67" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E67" s="10">
         <v>100</v>
@@ -2651,14 +2651,14 @@
     </row>
     <row r="68" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E68" s="11">
         <v>222</v>
@@ -2673,14 +2673,14 @@
     </row>
     <row r="69" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E69" s="10">
         <v>150</v>
@@ -2695,14 +2695,14 @@
     </row>
     <row r="70" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E70" s="11">
         <v>500</v>
@@ -2717,14 +2717,14 @@
     </row>
     <row r="71" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E71" s="10">
         <v>500</v>
@@ -2739,14 +2739,14 @@
     </row>
     <row r="72" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E72" s="11">
         <v>700</v>
@@ -2761,14 +2761,14 @@
     </row>
     <row r="73" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E73" s="10">
         <v>3000</v>
@@ -2792,7 +2792,7 @@
         <v>101</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E74" s="11">
         <v>200</v>
@@ -2816,7 +2816,7 @@
         <v>101</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E75" s="10">
         <v>200</v>
@@ -2831,14 +2831,14 @@
     </row>
     <row r="76" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>127</v>
+        <v>228</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E76" s="11">
         <v>200</v>
@@ -2853,14 +2853,14 @@
     </row>
     <row r="77" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E77" s="10">
         <v>11</v>
@@ -2875,14 +2875,14 @@
     </row>
     <row r="78" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E78" s="11">
         <v>169</v>
@@ -2906,7 +2906,7 @@
         <v>112</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E79" s="10">
         <v>26</v>
@@ -2921,14 +2921,14 @@
     </row>
     <row r="80" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E80" s="11">
         <v>119</v>
@@ -2943,14 +2943,14 @@
     </row>
     <row r="81" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E81" s="10">
         <v>200</v>
@@ -2965,14 +2965,14 @@
     </row>
     <row r="82" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E82" s="11">
         <v>250</v>
@@ -2987,14 +2987,14 @@
     </row>
     <row r="83" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E83" s="10">
         <v>384</v>
@@ -3009,14 +3009,14 @@
     </row>
     <row r="84" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E84" s="11">
         <v>235</v>
@@ -3031,14 +3031,14 @@
     </row>
     <row r="85" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E85" s="10">
         <v>508</v>
@@ -3053,14 +3053,14 @@
     </row>
     <row r="86" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E86" s="11">
         <v>200</v>
@@ -3075,14 +3075,14 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E87" s="10">
         <v>50</v>
@@ -3097,14 +3097,14 @@
     </row>
     <row r="88" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E88" s="11">
         <v>20</v>
@@ -3119,14 +3119,14 @@
     </row>
     <row r="89" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E89" s="10">
         <v>315</v>
@@ -3141,14 +3141,14 @@
     </row>
     <row r="90" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E90" s="11">
         <v>2600</v>
@@ -3163,14 +3163,14 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E91" s="10">
         <v>1000</v>
@@ -3185,14 +3185,14 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E92" s="11">
         <v>1402</v>
@@ -3207,14 +3207,14 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E93" s="10">
         <v>109</v>
@@ -3229,14 +3229,14 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E94" s="11">
         <v>151</v>
@@ -3251,14 +3251,14 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E95" s="10">
         <v>267</v>
@@ -3273,14 +3273,14 @@
     </row>
     <row r="96" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E96" s="11">
         <v>200</v>
@@ -3295,14 +3295,14 @@
     </row>
     <row r="97" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E97" s="10">
         <v>603</v>
@@ -3317,14 +3317,14 @@
     </row>
     <row r="98" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E98" s="11">
         <v>700</v>
@@ -3339,14 +3339,14 @@
     </row>
     <row r="99" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E99" s="10">
         <v>100</v>
@@ -3361,14 +3361,14 @@
     </row>
     <row r="100" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E100" s="11">
         <v>500</v>
@@ -3383,14 +3383,14 @@
     </row>
     <row r="101" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E101" s="10">
         <v>10</v>
@@ -3405,14 +3405,14 @@
     </row>
     <row r="102" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E102" s="11">
         <v>17</v>
@@ -3427,14 +3427,14 @@
     </row>
     <row r="103" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E103" s="10">
         <v>6</v>
@@ -3458,7 +3458,7 @@
         <v>104.2</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E104" s="11">
         <v>48</v>
@@ -3473,14 +3473,14 @@
     </row>
     <row r="105" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E105" s="10">
         <v>159</v>
@@ -3495,14 +3495,14 @@
     </row>
     <row r="106" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E106" s="11">
         <v>100</v>
@@ -3517,14 +3517,14 @@
     </row>
     <row r="107" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E107" s="10">
         <v>254</v>
@@ -3539,14 +3539,14 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E108" s="11">
         <v>15</v>
@@ -3561,14 +3561,14 @@
     </row>
     <row r="109" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E109" s="10">
         <v>200</v>
@@ -3580,19 +3580,19 @@
         <v>15.95</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E110" s="11">
         <v>95</v>
@@ -3607,14 +3607,14 @@
     </row>
     <row r="111" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E111" s="10">
         <v>165</v>
@@ -3629,14 +3629,14 @@
     </row>
     <row r="112" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E112" s="11">
         <v>100</v>
@@ -3660,7 +3660,7 @@
         <v>104.5</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E113" s="12">
         <v>6</v>
@@ -3672,19 +3672,19 @@
         <v>27</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E114" s="11">
         <v>300</v>
@@ -3698,14 +3698,14 @@
     </row>
     <row r="115" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E115" s="10">
         <v>350</v>
@@ -3719,14 +3719,14 @@
     </row>
     <row r="116" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E116" s="11">
         <v>200</v>
@@ -3740,14 +3740,14 @@
     </row>
     <row r="117" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E117" s="10">
         <v>100</v>
@@ -3770,7 +3770,7 @@
         <v>103.5</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E118" s="11">
         <v>100</v>
@@ -3793,7 +3793,7 @@
         <v>103.5</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E119" s="10">
         <v>200</v>
@@ -3807,14 +3807,14 @@
     </row>
     <row r="120" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E120" s="11">
         <v>210</v>
@@ -3828,14 +3828,14 @@
     </row>
     <row r="121" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E121" s="10">
         <v>210</v>
@@ -3849,14 +3849,14 @@
     </row>
     <row r="122" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E122" s="11">
         <v>3</v>
@@ -3870,14 +3870,14 @@
     </row>
     <row r="123" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E123" s="10">
         <v>10</v>
@@ -3900,7 +3900,7 @@
         <v>107</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E124" s="10">
         <v>200</v>
@@ -3914,14 +3914,14 @@
     </row>
     <row r="125" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E125" s="11">
         <v>52</v>
@@ -3935,14 +3935,14 @@
     </row>
     <row r="126" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E126" s="11">
         <v>50</v>
@@ -3956,14 +3956,14 @@
     </row>
     <row r="127" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E127" s="10">
         <v>200</v>
@@ -3977,14 +3977,14 @@
     </row>
     <row r="128" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C128" s="9"/>
       <c r="D128" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E128" s="11">
         <v>400</v>
@@ -3998,14 +3998,14 @@
     </row>
     <row r="129" spans="1:7" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E129" s="10">
         <v>200</v>
@@ -4019,14 +4019,14 @@
     </row>
     <row r="130" spans="1:7" ht="57" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E130" s="11">
         <v>86</v>
@@ -4040,14 +4040,14 @@
     </row>
     <row r="131" spans="1:7" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E131" s="10">
         <v>100</v>

--- a/Bonds/bonds.xlsx
+++ b/Bonds/bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ilya\Documents\GitHub\projects\Bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FAA236-70F9-43D1-8568-7CAD7D0FA084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D886AC9-A089-444B-AD21-569CC1412C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C1DB8464-260E-4338-9640-726B3E736107}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>Облигации Эфферон 001 Р-01 RU000A10CH03 на 3 года под 22% с выплатой купонов раз в квартал. Без амортизации и оферты</t>
   </si>
   <si>
-    <t>RU000A10СНОЗ</t>
-  </si>
-  <si>
     <t>СКС Ломбард БО-02 (СКСЛомб-БО-02) под 27% ежм на 3 года (Оферта Колл через 1.5 года - 16.03.27. Погашение 06.09.28. Только для квалифицированных инвесторов) !!! СПЕКУЛЯТИВНО !!!</t>
   </si>
   <si>
@@ -715,6 +712,9 @@
   </si>
   <si>
     <t>RU000A10D2Q2</t>
+  </si>
+  <si>
+    <t>RU000A10СН0З</t>
   </si>
 </sst>
 </file>
@@ -1157,37 +1157,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E2" s="10">
         <v>100</v>
@@ -1211,7 +1211,7 @@
         <v>103.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E3" s="11">
         <v>136</v>
@@ -1223,22 +1223,22 @@
         <v>23.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E4" s="10">
         <v>900</v>
@@ -1253,14 +1253,14 @@
     </row>
     <row r="5" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E5" s="11">
         <v>400</v>
@@ -1275,14 +1275,14 @@
     </row>
     <row r="6" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E6" s="11">
         <v>30</v>
@@ -1297,14 +1297,14 @@
     </row>
     <row r="7" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E7" s="10">
         <v>100</v>
@@ -1319,14 +1319,14 @@
     </row>
     <row r="8" spans="1:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E8" s="11">
         <v>203</v>
@@ -1338,7 +1338,7 @@
         <v>15.971</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
@@ -1352,7 +1352,7 @@
         <v>103.5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E9" s="10">
         <v>300</v>
@@ -1365,19 +1365,19 @@
       </c>
       <c r="H9" s="8"/>
       <c r="I9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E10" s="11">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>103.5</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E11" s="10">
         <v>149</v>
@@ -1414,15 +1414,15 @@
       </c>
       <c r="H11" s="8"/>
       <c r="I11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -1459,14 +1459,14 @@
     </row>
     <row r="14" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E14" s="10">
         <v>200</v>
@@ -1481,14 +1481,14 @@
     </row>
     <row r="15" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E15" s="11">
         <v>300</v>
@@ -1503,14 +1503,14 @@
     </row>
     <row r="16" spans="1:9" ht="57" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E16" s="10">
         <v>500</v>
@@ -1525,14 +1525,14 @@
     </row>
     <row r="17" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E17" s="11">
         <v>300</v>
@@ -1547,14 +1547,14 @@
     </row>
     <row r="18" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E18" s="10">
         <v>200</v>
@@ -1569,14 +1569,14 @@
     </row>
     <row r="19" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E19" s="11">
         <v>200</v>
@@ -1591,14 +1591,14 @@
     </row>
     <row r="20" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E20" s="10">
         <v>29</v>
@@ -1610,19 +1610,19 @@
         <v>17.311</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E21" s="11">
         <v>300</v>
@@ -1634,19 +1634,19 @@
         <v>17</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E22" s="10">
         <v>300</v>
@@ -1658,19 +1658,19 @@
         <v>17</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E23" s="11">
         <v>500</v>
@@ -1682,19 +1682,19 @@
         <v>17</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E24" s="10">
         <v>80</v>
@@ -1709,14 +1709,14 @@
     </row>
     <row r="25" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E25" s="11">
         <v>160</v>
@@ -1731,14 +1731,14 @@
     </row>
     <row r="26" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E26" s="10">
         <v>1</v>
@@ -1753,14 +1753,14 @@
     </row>
     <row r="27" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E27" s="11">
         <v>5</v>
@@ -1775,14 +1775,14 @@
     </row>
     <row r="28" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E28" s="10">
         <v>50</v>
@@ -1797,14 +1797,14 @@
     </row>
     <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E29" s="11">
         <v>417</v>
@@ -1816,19 +1816,19 @@
         <v>16.5</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E30" s="10">
         <v>300</v>
@@ -1843,14 +1843,14 @@
     </row>
     <row r="31" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E31" s="11">
         <v>23</v>
@@ -1865,14 +1865,14 @@
     </row>
     <row r="32" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E32" s="10">
         <v>500</v>
@@ -1887,14 +1887,14 @@
     </row>
     <row r="33" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E33" s="11">
         <v>9</v>
@@ -1909,14 +1909,14 @@
     </row>
     <row r="34" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E34" s="10">
         <v>500</v>
@@ -1931,14 +1931,14 @@
     </row>
     <row r="35" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E35" s="11">
         <v>400</v>
@@ -1953,14 +1953,14 @@
     </row>
     <row r="36" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E36" s="10">
         <v>34</v>
@@ -1984,7 +1984,7 @@
         <v>104.5</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E37" s="11">
         <v>330</v>
@@ -1999,14 +1999,14 @@
     </row>
     <row r="38" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="10">
         <v>22</v>
@@ -2021,14 +2021,14 @@
     </row>
     <row r="39" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E39" s="11">
         <v>200</v>
@@ -2043,14 +2043,14 @@
     </row>
     <row r="40" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E40" s="10">
         <v>200</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -2125,10 +2125,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -2165,14 +2165,14 @@
     </row>
     <row r="46" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E46" s="11">
         <v>100</v>
@@ -2187,14 +2187,14 @@
     </row>
     <row r="47" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E47" s="10">
         <v>23</v>
@@ -2209,14 +2209,14 @@
     </row>
     <row r="48" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E48" s="11">
         <v>1</v>
@@ -2231,14 +2231,14 @@
     </row>
     <row r="49" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E49" s="10">
         <v>31</v>
@@ -2253,14 +2253,14 @@
     </row>
     <row r="50" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E50" s="11">
         <v>170</v>
@@ -2275,14 +2275,14 @@
     </row>
     <row r="51" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E51" s="10">
         <v>180</v>
@@ -2294,19 +2294,19 @@
         <v>17.3</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E52" s="11">
         <v>10</v>
@@ -2321,14 +2321,14 @@
     </row>
     <row r="53" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E53" s="10">
         <v>200</v>
@@ -2343,14 +2343,14 @@
     </row>
     <row r="54" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E54" s="11">
         <v>400</v>
@@ -2365,14 +2365,14 @@
     </row>
     <row r="55" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E55" s="10">
         <v>300</v>
@@ -2387,14 +2387,14 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E56" s="11">
         <v>733</v>
@@ -2409,14 +2409,14 @@
     </row>
     <row r="57" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E57" s="10">
         <v>50</v>
@@ -2431,14 +2431,14 @@
     </row>
     <row r="58" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E58" s="11">
         <v>100</v>
@@ -2453,14 +2453,14 @@
     </row>
     <row r="59" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E59" s="10">
         <v>33</v>
@@ -2475,14 +2475,14 @@
     </row>
     <row r="60" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E60" s="11">
         <v>8</v>
@@ -2497,14 +2497,14 @@
     </row>
     <row r="61" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E61" s="10">
         <v>6</v>
@@ -2519,14 +2519,14 @@
     </row>
     <row r="62" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E62" s="11">
         <v>35</v>
@@ -2541,14 +2541,14 @@
     </row>
     <row r="63" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E63" s="10">
         <v>148</v>
@@ -2563,14 +2563,14 @@
     </row>
     <row r="64" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E64" s="11">
         <v>223</v>
@@ -2585,14 +2585,14 @@
     </row>
     <row r="65" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E65" s="10">
         <v>100</v>
@@ -2607,14 +2607,14 @@
     </row>
     <row r="66" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E66" s="11">
         <v>300</v>
@@ -2629,14 +2629,14 @@
     </row>
     <row r="67" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E67" s="10">
         <v>100</v>
@@ -2651,14 +2651,14 @@
     </row>
     <row r="68" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E68" s="11">
         <v>222</v>
@@ -2673,14 +2673,14 @@
     </row>
     <row r="69" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E69" s="10">
         <v>150</v>
@@ -2695,14 +2695,14 @@
     </row>
     <row r="70" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E70" s="11">
         <v>500</v>
@@ -2717,14 +2717,14 @@
     </row>
     <row r="71" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E71" s="10">
         <v>500</v>
@@ -2739,14 +2739,14 @@
     </row>
     <row r="72" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E72" s="11">
         <v>700</v>
@@ -2761,14 +2761,14 @@
     </row>
     <row r="73" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E73" s="10">
         <v>3000</v>
@@ -2792,7 +2792,7 @@
         <v>101</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E74" s="11">
         <v>200</v>
@@ -2816,7 +2816,7 @@
         <v>101</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E75" s="10">
         <v>200</v>
@@ -2831,14 +2831,14 @@
     </row>
     <row r="76" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E76" s="11">
         <v>200</v>
@@ -2853,14 +2853,14 @@
     </row>
     <row r="77" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E77" s="10">
         <v>11</v>
@@ -2875,14 +2875,14 @@
     </row>
     <row r="78" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E78" s="11">
         <v>169</v>
@@ -2906,7 +2906,7 @@
         <v>112</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E79" s="10">
         <v>26</v>
@@ -2921,14 +2921,14 @@
     </row>
     <row r="80" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E80" s="11">
         <v>119</v>
@@ -2943,14 +2943,14 @@
     </row>
     <row r="81" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E81" s="10">
         <v>200</v>
@@ -2965,14 +2965,14 @@
     </row>
     <row r="82" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E82" s="11">
         <v>250</v>
@@ -2987,14 +2987,14 @@
     </row>
     <row r="83" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E83" s="10">
         <v>384</v>
@@ -3009,14 +3009,14 @@
     </row>
     <row r="84" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E84" s="11">
         <v>235</v>
@@ -3031,14 +3031,14 @@
     </row>
     <row r="85" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E85" s="10">
         <v>508</v>
@@ -3053,14 +3053,14 @@
     </row>
     <row r="86" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E86" s="11">
         <v>200</v>
@@ -3075,14 +3075,14 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E87" s="10">
         <v>50</v>
@@ -3097,14 +3097,14 @@
     </row>
     <row r="88" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E88" s="11">
         <v>20</v>
@@ -3119,14 +3119,14 @@
     </row>
     <row r="89" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E89" s="10">
         <v>315</v>
@@ -3141,14 +3141,14 @@
     </row>
     <row r="90" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E90" s="11">
         <v>2600</v>
@@ -3163,14 +3163,14 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E91" s="10">
         <v>1000</v>
@@ -3185,14 +3185,14 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E92" s="11">
         <v>1402</v>
@@ -3207,14 +3207,14 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E93" s="10">
         <v>109</v>
@@ -3229,14 +3229,14 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E94" s="11">
         <v>151</v>
@@ -3251,14 +3251,14 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E95" s="10">
         <v>267</v>
@@ -3273,14 +3273,14 @@
     </row>
     <row r="96" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E96" s="11">
         <v>200</v>
@@ -3295,14 +3295,14 @@
     </row>
     <row r="97" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E97" s="10">
         <v>603</v>
@@ -3317,14 +3317,14 @@
     </row>
     <row r="98" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E98" s="11">
         <v>700</v>
@@ -3339,14 +3339,14 @@
     </row>
     <row r="99" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E99" s="10">
         <v>100</v>
@@ -3361,14 +3361,14 @@
     </row>
     <row r="100" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E100" s="11">
         <v>500</v>
@@ -3383,14 +3383,14 @@
     </row>
     <row r="101" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E101" s="10">
         <v>10</v>
@@ -3405,14 +3405,14 @@
     </row>
     <row r="102" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E102" s="11">
         <v>17</v>
@@ -3427,14 +3427,14 @@
     </row>
     <row r="103" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E103" s="10">
         <v>6</v>
@@ -3452,13 +3452,13 @@
         <v>14</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>15</v>
+        <v>229</v>
       </c>
       <c r="C104" s="3">
         <v>104.2</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E104" s="11">
         <v>48</v>
@@ -3473,14 +3473,14 @@
     </row>
     <row r="105" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E105" s="10">
         <v>159</v>
@@ -3495,14 +3495,14 @@
     </row>
     <row r="106" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E106" s="11">
         <v>100</v>
@@ -3517,14 +3517,14 @@
     </row>
     <row r="107" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E107" s="10">
         <v>254</v>
@@ -3539,14 +3539,14 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E108" s="11">
         <v>15</v>
@@ -3561,14 +3561,14 @@
     </row>
     <row r="109" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E109" s="10">
         <v>200</v>
@@ -3580,19 +3580,19 @@
         <v>15.95</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E110" s="11">
         <v>95</v>
@@ -3607,14 +3607,14 @@
     </row>
     <row r="111" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E111" s="10">
         <v>165</v>
@@ -3629,14 +3629,14 @@
     </row>
     <row r="112" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E112" s="11">
         <v>100</v>
@@ -3651,16 +3651,16 @@
     </row>
     <row r="113" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="C113" s="7">
         <v>104.5</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E113" s="12">
         <v>6</v>
@@ -3672,19 +3672,19 @@
         <v>27</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E114" s="11">
         <v>300</v>
@@ -3698,14 +3698,14 @@
     </row>
     <row r="115" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E115" s="10">
         <v>350</v>
@@ -3719,14 +3719,14 @@
     </row>
     <row r="116" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E116" s="11">
         <v>200</v>
@@ -3740,14 +3740,14 @@
     </row>
     <row r="117" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E117" s="10">
         <v>100</v>
@@ -3761,16 +3761,16 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="C118" s="3">
         <v>103.5</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E118" s="11">
         <v>100</v>
@@ -3784,16 +3784,16 @@
     </row>
     <row r="119" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C119" s="5">
         <v>103.5</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E119" s="10">
         <v>200</v>
@@ -3807,14 +3807,14 @@
     </row>
     <row r="120" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E120" s="11">
         <v>210</v>
@@ -3828,14 +3828,14 @@
     </row>
     <row r="121" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E121" s="10">
         <v>210</v>
@@ -3849,14 +3849,14 @@
     </row>
     <row r="122" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E122" s="11">
         <v>3</v>
@@ -3870,14 +3870,14 @@
     </row>
     <row r="123" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E123" s="10">
         <v>10</v>
@@ -3891,16 +3891,16 @@
     </row>
     <row r="124" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C124" s="5">
         <v>107</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E124" s="10">
         <v>200</v>
@@ -3914,14 +3914,14 @@
     </row>
     <row r="125" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E125" s="11">
         <v>52</v>
@@ -3935,14 +3935,14 @@
     </row>
     <row r="126" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E126" s="11">
         <v>50</v>
@@ -3956,14 +3956,14 @@
     </row>
     <row r="127" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E127" s="10">
         <v>200</v>
@@ -3977,14 +3977,14 @@
     </row>
     <row r="128" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="C128" s="9"/>
       <c r="D128" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E128" s="11">
         <v>400</v>
@@ -3998,14 +3998,14 @@
     </row>
     <row r="129" spans="1:7" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E129" s="10">
         <v>200</v>
@@ -4019,14 +4019,14 @@
     </row>
     <row r="130" spans="1:7" ht="57" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E130" s="11">
         <v>86</v>
@@ -4040,14 +4040,14 @@
     </row>
     <row r="131" spans="1:7" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E131" s="10">
         <v>100</v>

--- a/Bonds/bonds.xlsx
+++ b/Bonds/bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ilya\Documents\GitHub\projects\Bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D886AC9-A089-444B-AD21-569CC1412C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB65A07B-4C52-48C5-A9F0-616858FEC1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C1DB8464-260E-4338-9640-726B3E736107}"/>
   </bookViews>
@@ -714,7 +714,7 @@
     <t>RU000A10D2Q2</t>
   </si>
   <si>
-    <t>RU000A10СН0З</t>
+    <t>RU000A10СН03</t>
   </si>
 </sst>
 </file>

--- a/Bonds/bonds.xlsx
+++ b/Bonds/bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ilya\Documents\GitHub\projects\Bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB65A07B-4C52-48C5-A9F0-616858FEC1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90A5587-888D-4232-BDE3-C1798AD3CDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C1DB8464-260E-4338-9640-726B3E736107}"/>
   </bookViews>
@@ -288,9 +288,6 @@
     <t>Кредитный Поток 3.0 RU000A10DBM5— это облигации, обеспеченные портфелем кредитных карт Т-Банка. Под 17,3% фикс ЕЖМ каждого 24 числа месяца на 25 месяцев. Оферта Call 24.12.27 на весь объём. При отсутствии оферты начнётся амортизация до 24.06.2030</t>
   </si>
   <si>
-    <t>RU000A0DBM5</t>
-  </si>
-  <si>
     <t>Магнит ПАО БО-005P-04 Рейтинг: ААА (АКРА, прогноз «Стабильный») Купон: КС+150 б.п. финальный (ежемесячный) Срок обращения: 2 года Объем: 10 млрд. Р Амортизация: нет Оферта: нет Номинал: 1000 Р</t>
   </si>
   <si>
@@ -715,6 +712,9 @@
   </si>
   <si>
     <t>RU000A10СН03</t>
+  </si>
+  <si>
+    <t>RU000A10DBM5</t>
   </si>
 </sst>
 </file>
@@ -1160,22 +1160,22 @@
         <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E2" s="10">
         <v>100</v>
@@ -1211,7 +1211,7 @@
         <v>103.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E3" s="11">
         <v>136</v>
@@ -1223,10 +1223,10 @@
         <v>23.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E4" s="10">
         <v>900</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E5" s="11">
         <v>400</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E6" s="11">
         <v>30</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E7" s="10">
         <v>100</v>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E8" s="11">
         <v>203</v>
@@ -1338,7 +1338,7 @@
         <v>15.971</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
@@ -1352,7 +1352,7 @@
         <v>103.5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E9" s="10">
         <v>300</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="H9" s="8"/>
       <c r="I9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E10" s="11">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>103.5</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E11" s="10">
         <v>149</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H11" s="8"/>
       <c r="I11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E14" s="10">
         <v>200</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E15" s="11">
         <v>300</v>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E16" s="10">
         <v>500</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E17" s="11">
         <v>300</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E18" s="10">
         <v>200</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E19" s="11">
         <v>200</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E20" s="10">
         <v>29</v>
@@ -1610,7 +1610,7 @@
         <v>17.311</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E21" s="11">
         <v>300</v>
@@ -1634,7 +1634,7 @@
         <v>17</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E22" s="10">
         <v>300</v>
@@ -1658,7 +1658,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E23" s="11">
         <v>500</v>
@@ -1682,7 +1682,7 @@
         <v>17</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E24" s="10">
         <v>80</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E25" s="11">
         <v>160</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E26" s="10">
         <v>1</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E27" s="11">
         <v>5</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E28" s="10">
         <v>50</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E29" s="11">
         <v>417</v>
@@ -1816,7 +1816,7 @@
         <v>16.5</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E30" s="10">
         <v>300</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E31" s="11">
         <v>23</v>
@@ -1868,11 +1868,11 @@
         <v>63</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E32" s="10">
         <v>500</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E33" s="11">
         <v>9</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E34" s="10">
         <v>500</v>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E35" s="11">
         <v>400</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E36" s="10">
         <v>34</v>
@@ -1984,7 +1984,7 @@
         <v>104.5</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E37" s="11">
         <v>330</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E38" s="10">
         <v>22</v>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E39" s="11">
         <v>200</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E40" s="10">
         <v>200</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E46" s="11">
         <v>100</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E47" s="10">
         <v>23</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E48" s="11">
         <v>1</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E49" s="10">
         <v>31</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E50" s="11">
         <v>170</v>
@@ -2278,11 +2278,11 @@
         <v>86</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E51" s="10">
         <v>180</v>
@@ -2294,19 +2294,19 @@
         <v>17.3</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E52" s="11">
         <v>10</v>
@@ -2321,14 +2321,14 @@
     </row>
     <row r="53" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E53" s="10">
         <v>200</v>
@@ -2343,14 +2343,14 @@
     </row>
     <row r="54" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E54" s="11">
         <v>400</v>
@@ -2365,14 +2365,14 @@
     </row>
     <row r="55" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E55" s="10">
         <v>300</v>
@@ -2387,14 +2387,14 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E56" s="11">
         <v>733</v>
@@ -2409,14 +2409,14 @@
     </row>
     <row r="57" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E57" s="10">
         <v>50</v>
@@ -2431,14 +2431,14 @@
     </row>
     <row r="58" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E58" s="11">
         <v>100</v>
@@ -2453,14 +2453,14 @@
     </row>
     <row r="59" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E59" s="10">
         <v>33</v>
@@ -2475,14 +2475,14 @@
     </row>
     <row r="60" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E60" s="11">
         <v>8</v>
@@ -2497,14 +2497,14 @@
     </row>
     <row r="61" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E61" s="10">
         <v>6</v>
@@ -2519,14 +2519,14 @@
     </row>
     <row r="62" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E62" s="11">
         <v>35</v>
@@ -2541,14 +2541,14 @@
     </row>
     <row r="63" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E63" s="10">
         <v>148</v>
@@ -2563,14 +2563,14 @@
     </row>
     <row r="64" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E64" s="11">
         <v>223</v>
@@ -2585,14 +2585,14 @@
     </row>
     <row r="65" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E65" s="10">
         <v>100</v>
@@ -2607,14 +2607,14 @@
     </row>
     <row r="66" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E66" s="11">
         <v>300</v>
@@ -2629,14 +2629,14 @@
     </row>
     <row r="67" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E67" s="10">
         <v>100</v>
@@ -2651,14 +2651,14 @@
     </row>
     <row r="68" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E68" s="11">
         <v>222</v>
@@ -2673,14 +2673,14 @@
     </row>
     <row r="69" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E69" s="10">
         <v>150</v>
@@ -2695,14 +2695,14 @@
     </row>
     <row r="70" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E70" s="11">
         <v>500</v>
@@ -2717,14 +2717,14 @@
     </row>
     <row r="71" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E71" s="10">
         <v>500</v>
@@ -2739,14 +2739,14 @@
     </row>
     <row r="72" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E72" s="11">
         <v>700</v>
@@ -2761,14 +2761,14 @@
     </row>
     <row r="73" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E73" s="10">
         <v>3000</v>
@@ -2792,7 +2792,7 @@
         <v>101</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E74" s="11">
         <v>200</v>
@@ -2816,7 +2816,7 @@
         <v>101</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E75" s="10">
         <v>200</v>
@@ -2831,14 +2831,14 @@
     </row>
     <row r="76" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E76" s="11">
         <v>200</v>
@@ -2853,14 +2853,14 @@
     </row>
     <row r="77" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E77" s="10">
         <v>11</v>
@@ -2875,14 +2875,14 @@
     </row>
     <row r="78" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E78" s="11">
         <v>169</v>
@@ -2906,7 +2906,7 @@
         <v>112</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E79" s="10">
         <v>26</v>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E80" s="11">
         <v>119</v>
@@ -2943,14 +2943,14 @@
     </row>
     <row r="81" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E81" s="10">
         <v>200</v>
@@ -2965,14 +2965,14 @@
     </row>
     <row r="82" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E82" s="11">
         <v>250</v>
@@ -2987,14 +2987,14 @@
     </row>
     <row r="83" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E83" s="10">
         <v>384</v>
@@ -3009,14 +3009,14 @@
     </row>
     <row r="84" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E84" s="11">
         <v>235</v>
@@ -3031,14 +3031,14 @@
     </row>
     <row r="85" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E85" s="10">
         <v>508</v>
@@ -3053,14 +3053,14 @@
     </row>
     <row r="86" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E86" s="11">
         <v>200</v>
@@ -3075,14 +3075,14 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E87" s="10">
         <v>50</v>
@@ -3097,14 +3097,14 @@
     </row>
     <row r="88" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E88" s="11">
         <v>20</v>
@@ -3119,14 +3119,14 @@
     </row>
     <row r="89" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E89" s="10">
         <v>315</v>
@@ -3141,14 +3141,14 @@
     </row>
     <row r="90" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E90" s="11">
         <v>2600</v>
@@ -3163,14 +3163,14 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E91" s="10">
         <v>1000</v>
@@ -3185,14 +3185,14 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E92" s="11">
         <v>1402</v>
@@ -3207,14 +3207,14 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E93" s="10">
         <v>109</v>
@@ -3229,14 +3229,14 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E94" s="11">
         <v>151</v>
@@ -3251,14 +3251,14 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E95" s="10">
         <v>267</v>
@@ -3273,14 +3273,14 @@
     </row>
     <row r="96" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E96" s="11">
         <v>200</v>
@@ -3295,14 +3295,14 @@
     </row>
     <row r="97" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E97" s="10">
         <v>603</v>
@@ -3317,14 +3317,14 @@
     </row>
     <row r="98" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E98" s="11">
         <v>700</v>
@@ -3339,14 +3339,14 @@
     </row>
     <row r="99" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E99" s="10">
         <v>100</v>
@@ -3361,14 +3361,14 @@
     </row>
     <row r="100" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E100" s="11">
         <v>500</v>
@@ -3383,14 +3383,14 @@
     </row>
     <row r="101" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E101" s="10">
         <v>10</v>
@@ -3405,14 +3405,14 @@
     </row>
     <row r="102" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E102" s="11">
         <v>17</v>
@@ -3427,14 +3427,14 @@
     </row>
     <row r="103" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E103" s="10">
         <v>6</v>
@@ -3452,13 +3452,13 @@
         <v>14</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C104" s="3">
         <v>104.2</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E104" s="11">
         <v>48</v>
@@ -3473,14 +3473,14 @@
     </row>
     <row r="105" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E105" s="10">
         <v>159</v>
@@ -3495,14 +3495,14 @@
     </row>
     <row r="106" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E106" s="11">
         <v>100</v>
@@ -3517,14 +3517,14 @@
     </row>
     <row r="107" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E107" s="10">
         <v>254</v>
@@ -3539,14 +3539,14 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E108" s="11">
         <v>15</v>
@@ -3561,14 +3561,14 @@
     </row>
     <row r="109" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E109" s="10">
         <v>200</v>
@@ -3580,19 +3580,19 @@
         <v>15.95</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E110" s="11">
         <v>95</v>
@@ -3607,14 +3607,14 @@
     </row>
     <row r="111" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E111" s="10">
         <v>165</v>
@@ -3629,14 +3629,14 @@
     </row>
     <row r="112" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E112" s="11">
         <v>100</v>
@@ -3660,7 +3660,7 @@
         <v>104.5</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E113" s="12">
         <v>6</v>
@@ -3672,19 +3672,19 @@
         <v>27</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E114" s="11">
         <v>300</v>
@@ -3698,14 +3698,14 @@
     </row>
     <row r="115" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E115" s="10">
         <v>350</v>
@@ -3719,14 +3719,14 @@
     </row>
     <row r="116" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E116" s="11">
         <v>200</v>
@@ -3740,14 +3740,14 @@
     </row>
     <row r="117" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E117" s="10">
         <v>100</v>
@@ -3770,7 +3770,7 @@
         <v>103.5</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E118" s="11">
         <v>100</v>
@@ -3793,7 +3793,7 @@
         <v>103.5</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E119" s="10">
         <v>200</v>
@@ -3807,14 +3807,14 @@
     </row>
     <row r="120" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E120" s="11">
         <v>210</v>
@@ -3828,14 +3828,14 @@
     </row>
     <row r="121" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E121" s="10">
         <v>210</v>
@@ -3849,14 +3849,14 @@
     </row>
     <row r="122" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E122" s="11">
         <v>3</v>
@@ -3870,14 +3870,14 @@
     </row>
     <row r="123" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E123" s="10">
         <v>10</v>
@@ -3900,7 +3900,7 @@
         <v>107</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E124" s="10">
         <v>200</v>
@@ -3914,14 +3914,14 @@
     </row>
     <row r="125" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E125" s="11">
         <v>52</v>
@@ -3935,14 +3935,14 @@
     </row>
     <row r="126" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E126" s="11">
         <v>50</v>
@@ -3956,14 +3956,14 @@
     </row>
     <row r="127" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E127" s="10">
         <v>200</v>
@@ -3977,14 +3977,14 @@
     </row>
     <row r="128" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="C128" s="9"/>
       <c r="D128" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E128" s="11">
         <v>400</v>
@@ -3998,14 +3998,14 @@
     </row>
     <row r="129" spans="1:7" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E129" s="10">
         <v>200</v>
@@ -4019,14 +4019,14 @@
     </row>
     <row r="130" spans="1:7" ht="57" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E130" s="11">
         <v>86</v>
@@ -4040,14 +4040,14 @@
     </row>
     <row r="131" spans="1:7" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E131" s="10">
         <v>100</v>

--- a/Bonds/bonds.xlsx
+++ b/Bonds/bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ilya\Documents\GitHub\projects\Bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90A5587-888D-4232-BDE3-C1798AD3CDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A73879-88C5-47F1-9E54-E476A35E2C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C1DB8464-260E-4338-9640-726B3E736107}"/>
   </bookViews>
@@ -177,9 +177,6 @@
     <t>Балтийский лизинг Б0-П19 АА- на 3 года. Первичное размещение под 17%. Выплата каждые 30 дней Оферта CALL 27.08.28. Дата погашения 21.08.35</t>
   </si>
   <si>
-    <t>RU000A10СС32</t>
-  </si>
-  <si>
     <t>ВТБ Лизинг 001Р-МБ-03 АА RU000A10CQE2 на 3 года. Первичное размещение под 15.5%. Выплата каждые 30 дней. Амортизация каждые 3 мес по 8.3%. Оферты нет</t>
   </si>
   <si>
@@ -711,10 +708,13 @@
     <t>RU000A10D2Q2</t>
   </si>
   <si>
-    <t>RU000A10СН03</t>
-  </si>
-  <si>
     <t>RU000A10DBM5</t>
+  </si>
+  <si>
+    <t>RU000A10CH03</t>
+  </si>
+  <si>
+    <t>RU000A10CC32</t>
   </si>
 </sst>
 </file>
@@ -790,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -827,6 +827,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1160,22 +1163,22 @@
         <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1187,7 +1190,7 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E2" s="10">
         <v>100</v>
@@ -1211,7 +1214,7 @@
         <v>103.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E3" s="11">
         <v>136</v>
@@ -1223,10 +1226,10 @@
         <v>23.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
@@ -1238,7 +1241,7 @@
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E4" s="10">
         <v>900</v>
@@ -1260,7 +1263,7 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E5" s="11">
         <v>400</v>
@@ -1282,7 +1285,7 @@
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E6" s="11">
         <v>30</v>
@@ -1304,7 +1307,7 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E7" s="10">
         <v>100</v>
@@ -1326,7 +1329,7 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E8" s="11">
         <v>203</v>
@@ -1338,7 +1341,7 @@
         <v>15.971</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
@@ -1352,7 +1355,7 @@
         <v>103.5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E9" s="10">
         <v>300</v>
@@ -1365,7 +1368,7 @@
       </c>
       <c r="H9" s="8"/>
       <c r="I9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -1377,7 +1380,7 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E10" s="11">
         <v>100</v>
@@ -1401,7 +1404,7 @@
         <v>103.5</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E11" s="10">
         <v>149</v>
@@ -1414,7 +1417,7 @@
       </c>
       <c r="H11" s="8"/>
       <c r="I11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1466,7 +1469,7 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E14" s="10">
         <v>200</v>
@@ -1488,7 +1491,7 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E15" s="11">
         <v>300</v>
@@ -1510,7 +1513,7 @@
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E16" s="10">
         <v>500</v>
@@ -1532,7 +1535,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E17" s="11">
         <v>300</v>
@@ -1554,7 +1557,7 @@
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E18" s="10">
         <v>200</v>
@@ -1576,7 +1579,7 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E19" s="11">
         <v>200</v>
@@ -1593,12 +1596,12 @@
       <c r="A20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>50</v>
+      <c r="B20" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E20" s="10">
         <v>29</v>
@@ -1610,19 +1613,19 @@
         <v>17.311</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>50</v>
+      <c r="B21" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E21" s="11">
         <v>300</v>
@@ -1634,19 +1637,19 @@
         <v>17</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>50</v>
+      <c r="B22" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E22" s="10">
         <v>300</v>
@@ -1658,19 +1661,19 @@
         <v>17</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>50</v>
+      <c r="B23" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E23" s="11">
         <v>500</v>
@@ -1682,19 +1685,19 @@
         <v>17</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E24" s="10">
         <v>80</v>
@@ -1709,14 +1712,14 @@
     </row>
     <row r="25" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E25" s="11">
         <v>160</v>
@@ -1731,14 +1734,14 @@
     </row>
     <row r="26" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E26" s="10">
         <v>1</v>
@@ -1753,14 +1756,14 @@
     </row>
     <row r="27" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E27" s="11">
         <v>5</v>
@@ -1775,14 +1778,14 @@
     </row>
     <row r="28" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E28" s="10">
         <v>50</v>
@@ -1797,14 +1800,14 @@
     </row>
     <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E29" s="11">
         <v>417</v>
@@ -1816,19 +1819,19 @@
         <v>16.5</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E30" s="10">
         <v>300</v>
@@ -1843,14 +1846,14 @@
     </row>
     <row r="31" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E31" s="11">
         <v>23</v>
@@ -1865,14 +1868,14 @@
     </row>
     <row r="32" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E32" s="10">
         <v>500</v>
@@ -1887,14 +1890,14 @@
     </row>
     <row r="33" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E33" s="11">
         <v>9</v>
@@ -1909,14 +1912,14 @@
     </row>
     <row r="34" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E34" s="10">
         <v>500</v>
@@ -1931,14 +1934,14 @@
     </row>
     <row r="35" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E35" s="11">
         <v>400</v>
@@ -1953,14 +1956,14 @@
     </row>
     <row r="36" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E36" s="10">
         <v>34</v>
@@ -1984,7 +1987,7 @@
         <v>104.5</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E37" s="11">
         <v>330</v>
@@ -1999,14 +2002,14 @@
     </row>
     <row r="38" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E38" s="10">
         <v>22</v>
@@ -2021,14 +2024,14 @@
     </row>
     <row r="39" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" s="11">
         <v>200</v>
@@ -2043,14 +2046,14 @@
     </row>
     <row r="40" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E40" s="10">
         <v>200</v>
@@ -2065,10 +2068,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -2085,10 +2088,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -2105,10 +2108,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -2125,10 +2128,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -2145,10 +2148,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -2165,14 +2168,14 @@
     </row>
     <row r="46" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E46" s="11">
         <v>100</v>
@@ -2187,14 +2190,14 @@
     </row>
     <row r="47" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E47" s="10">
         <v>23</v>
@@ -2209,14 +2212,14 @@
     </row>
     <row r="48" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E48" s="11">
         <v>1</v>
@@ -2231,14 +2234,14 @@
     </row>
     <row r="49" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E49" s="10">
         <v>31</v>
@@ -2253,14 +2256,14 @@
     </row>
     <row r="50" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E50" s="11">
         <v>170</v>
@@ -2275,14 +2278,14 @@
     </row>
     <row r="51" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E51" s="10">
         <v>180</v>
@@ -2294,19 +2297,19 @@
         <v>17.3</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E52" s="11">
         <v>10</v>
@@ -2321,14 +2324,14 @@
     </row>
     <row r="53" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E53" s="10">
         <v>200</v>
@@ -2343,14 +2346,14 @@
     </row>
     <row r="54" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E54" s="11">
         <v>400</v>
@@ -2365,14 +2368,14 @@
     </row>
     <row r="55" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E55" s="10">
         <v>300</v>
@@ -2387,14 +2390,14 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E56" s="11">
         <v>733</v>
@@ -2409,14 +2412,14 @@
     </row>
     <row r="57" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E57" s="10">
         <v>50</v>
@@ -2431,14 +2434,14 @@
     </row>
     <row r="58" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E58" s="11">
         <v>100</v>
@@ -2453,14 +2456,14 @@
     </row>
     <row r="59" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E59" s="10">
         <v>33</v>
@@ -2475,14 +2478,14 @@
     </row>
     <row r="60" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E60" s="11">
         <v>8</v>
@@ -2497,14 +2500,14 @@
     </row>
     <row r="61" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E61" s="10">
         <v>6</v>
@@ -2519,14 +2522,14 @@
     </row>
     <row r="62" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E62" s="11">
         <v>35</v>
@@ -2541,14 +2544,14 @@
     </row>
     <row r="63" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E63" s="10">
         <v>148</v>
@@ -2563,14 +2566,14 @@
     </row>
     <row r="64" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E64" s="11">
         <v>223</v>
@@ -2585,14 +2588,14 @@
     </row>
     <row r="65" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E65" s="10">
         <v>100</v>
@@ -2607,14 +2610,14 @@
     </row>
     <row r="66" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E66" s="11">
         <v>300</v>
@@ -2629,14 +2632,14 @@
     </row>
     <row r="67" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E67" s="10">
         <v>100</v>
@@ -2651,14 +2654,14 @@
     </row>
     <row r="68" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E68" s="11">
         <v>222</v>
@@ -2673,14 +2676,14 @@
     </row>
     <row r="69" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E69" s="10">
         <v>150</v>
@@ -2695,14 +2698,14 @@
     </row>
     <row r="70" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E70" s="11">
         <v>500</v>
@@ -2717,14 +2720,14 @@
     </row>
     <row r="71" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E71" s="10">
         <v>500</v>
@@ -2739,14 +2742,14 @@
     </row>
     <row r="72" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E72" s="11">
         <v>700</v>
@@ -2761,14 +2764,14 @@
     </row>
     <row r="73" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E73" s="10">
         <v>3000</v>
@@ -2792,7 +2795,7 @@
         <v>101</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E74" s="11">
         <v>200</v>
@@ -2816,7 +2819,7 @@
         <v>101</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E75" s="10">
         <v>200</v>
@@ -2831,14 +2834,14 @@
     </row>
     <row r="76" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E76" s="11">
         <v>200</v>
@@ -2853,14 +2856,14 @@
     </row>
     <row r="77" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E77" s="10">
         <v>11</v>
@@ -2875,14 +2878,14 @@
     </row>
     <row r="78" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E78" s="11">
         <v>169</v>
@@ -2906,7 +2909,7 @@
         <v>112</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E79" s="10">
         <v>26</v>
@@ -2921,14 +2924,14 @@
     </row>
     <row r="80" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E80" s="11">
         <v>119</v>
@@ -2943,14 +2946,14 @@
     </row>
     <row r="81" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E81" s="10">
         <v>200</v>
@@ -2965,14 +2968,14 @@
     </row>
     <row r="82" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E82" s="11">
         <v>250</v>
@@ -2987,14 +2990,14 @@
     </row>
     <row r="83" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E83" s="10">
         <v>384</v>
@@ -3009,14 +3012,14 @@
     </row>
     <row r="84" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E84" s="11">
         <v>235</v>
@@ -3031,14 +3034,14 @@
     </row>
     <row r="85" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E85" s="10">
         <v>508</v>
@@ -3053,14 +3056,14 @@
     </row>
     <row r="86" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E86" s="11">
         <v>200</v>
@@ -3075,14 +3078,14 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E87" s="10">
         <v>50</v>
@@ -3097,14 +3100,14 @@
     </row>
     <row r="88" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E88" s="11">
         <v>20</v>
@@ -3119,14 +3122,14 @@
     </row>
     <row r="89" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E89" s="10">
         <v>315</v>
@@ -3141,14 +3144,14 @@
     </row>
     <row r="90" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E90" s="11">
         <v>2600</v>
@@ -3163,14 +3166,14 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E91" s="10">
         <v>1000</v>
@@ -3185,14 +3188,14 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E92" s="11">
         <v>1402</v>
@@ -3207,14 +3210,14 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E93" s="10">
         <v>109</v>
@@ -3229,14 +3232,14 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E94" s="11">
         <v>151</v>
@@ -3251,14 +3254,14 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E95" s="10">
         <v>267</v>
@@ -3273,14 +3276,14 @@
     </row>
     <row r="96" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E96" s="11">
         <v>200</v>
@@ -3295,14 +3298,14 @@
     </row>
     <row r="97" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E97" s="10">
         <v>603</v>
@@ -3317,14 +3320,14 @@
     </row>
     <row r="98" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E98" s="11">
         <v>700</v>
@@ -3339,14 +3342,14 @@
     </row>
     <row r="99" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E99" s="10">
         <v>100</v>
@@ -3361,14 +3364,14 @@
     </row>
     <row r="100" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E100" s="11">
         <v>500</v>
@@ -3383,14 +3386,14 @@
     </row>
     <row r="101" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E101" s="10">
         <v>10</v>
@@ -3405,14 +3408,14 @@
     </row>
     <row r="102" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E102" s="11">
         <v>17</v>
@@ -3427,14 +3430,14 @@
     </row>
     <row r="103" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E103" s="10">
         <v>6</v>
@@ -3458,7 +3461,7 @@
         <v>104.2</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E104" s="11">
         <v>48</v>
@@ -3473,14 +3476,14 @@
     </row>
     <row r="105" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E105" s="10">
         <v>159</v>
@@ -3495,14 +3498,14 @@
     </row>
     <row r="106" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E106" s="11">
         <v>100</v>
@@ -3517,14 +3520,14 @@
     </row>
     <row r="107" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E107" s="10">
         <v>254</v>
@@ -3539,14 +3542,14 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E108" s="11">
         <v>15</v>
@@ -3561,14 +3564,14 @@
     </row>
     <row r="109" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E109" s="10">
         <v>200</v>
@@ -3580,19 +3583,19 @@
         <v>15.95</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E110" s="11">
         <v>95</v>
@@ -3607,14 +3610,14 @@
     </row>
     <row r="111" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E111" s="10">
         <v>165</v>
@@ -3629,14 +3632,14 @@
     </row>
     <row r="112" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E112" s="11">
         <v>100</v>
@@ -3660,7 +3663,7 @@
         <v>104.5</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E113" s="12">
         <v>6</v>
@@ -3672,19 +3675,19 @@
         <v>27</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E114" s="11">
         <v>300</v>
@@ -3698,14 +3701,14 @@
     </row>
     <row r="115" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E115" s="10">
         <v>350</v>
@@ -3719,14 +3722,14 @@
     </row>
     <row r="116" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E116" s="11">
         <v>200</v>
@@ -3740,14 +3743,14 @@
     </row>
     <row r="117" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E117" s="10">
         <v>100</v>
@@ -3770,7 +3773,7 @@
         <v>103.5</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E118" s="11">
         <v>100</v>
@@ -3793,7 +3796,7 @@
         <v>103.5</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E119" s="10">
         <v>200</v>
@@ -3807,14 +3810,14 @@
     </row>
     <row r="120" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E120" s="11">
         <v>210</v>
@@ -3828,14 +3831,14 @@
     </row>
     <row r="121" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E121" s="10">
         <v>210</v>
@@ -3849,14 +3852,14 @@
     </row>
     <row r="122" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E122" s="11">
         <v>3</v>
@@ -3870,14 +3873,14 @@
     </row>
     <row r="123" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E123" s="10">
         <v>10</v>
@@ -3900,7 +3903,7 @@
         <v>107</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E124" s="10">
         <v>200</v>
@@ -3914,14 +3917,14 @@
     </row>
     <row r="125" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E125" s="11">
         <v>52</v>
@@ -3935,14 +3938,14 @@
     </row>
     <row r="126" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E126" s="11">
         <v>50</v>
@@ -3956,14 +3959,14 @@
     </row>
     <row r="127" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E127" s="10">
         <v>200</v>
@@ -3977,14 +3980,14 @@
     </row>
     <row r="128" spans="1:8" ht="57" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="C128" s="9"/>
       <c r="D128" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E128" s="11">
         <v>400</v>
@@ -3998,14 +4001,14 @@
     </row>
     <row r="129" spans="1:7" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E129" s="10">
         <v>200</v>
@@ -4019,14 +4022,14 @@
     </row>
     <row r="130" spans="1:7" ht="57" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E130" s="11">
         <v>86</v>
@@ -4040,14 +4043,14 @@
     </row>
     <row r="131" spans="1:7" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E131" s="10">
         <v>100</v>
